--- a/ADB1 Sheets/output_city_wise.xlsx
+++ b/ADB1 Sheets/output_city_wise.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="674">
   <si>
     <t>city</t>
   </si>
@@ -85,76 +85,88 @@
     <t>shop_ca_consumed_sqft_igr</t>
   </si>
   <si>
-    <t>1.5bhk_sold_igr</t>
-  </si>
-  <si>
-    <t>1bhk_sold_igr</t>
-  </si>
-  <si>
-    <t>2.5bhk_sold_igr</t>
-  </si>
-  <si>
-    <t>2bhk_sold_igr</t>
-  </si>
-  <si>
-    <t>3bhk_sold_igr</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_sold_igr</t>
-  </si>
-  <si>
-    <t>1.5bhk_total_agreement_price</t>
-  </si>
-  <si>
-    <t>1bhk_total_agreement_price</t>
-  </si>
-  <si>
-    <t>2.5bhk_total_agreement_price</t>
-  </si>
-  <si>
-    <t>2bhk_total_agreement_price</t>
-  </si>
-  <si>
-    <t>3bhk_total_agreement_price</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_total_agreement_price</t>
-  </si>
-  <si>
-    <t>1.5bhk_avg_agreement_price</t>
-  </si>
-  <si>
-    <t>1bhk_avg_agreement_price</t>
-  </si>
-  <si>
-    <t>2.5bhk_avg_agreement_price</t>
-  </si>
-  <si>
-    <t>2bhk_avg_agreement_price</t>
-  </si>
-  <si>
-    <t>3bhk_avg_agreement_price</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_avg_agreement_price</t>
-  </si>
-  <si>
-    <t>1.5bhk_ca_consumed_sqft_igr</t>
-  </si>
-  <si>
-    <t>1bhk_ca_consumed_sqft_igr</t>
-  </si>
-  <si>
-    <t>2.5bhk_ca_consumed_sqft_igr</t>
-  </si>
-  <si>
-    <t>2bhk_ca_consumed_sqft_igr</t>
-  </si>
-  <si>
-    <t>3bhk_ca_consumed_sqft_igr</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_ca_consumed_sqft_igr</t>
+    <t>1.5br_sold_igr</t>
+  </si>
+  <si>
+    <t>1br_sold_igr</t>
+  </si>
+  <si>
+    <t>2.5br_sold_igr</t>
+  </si>
+  <si>
+    <t>2br_sold_igr</t>
+  </si>
+  <si>
+    <t>3br_sold_igr</t>
+  </si>
+  <si>
+    <t>4br_sold_igr</t>
+  </si>
+  <si>
+    <t>&gt;3br_sold_igr</t>
+  </si>
+  <si>
+    <t>1.5br_total_agreement_price</t>
+  </si>
+  <si>
+    <t>1br_total_agreement_price</t>
+  </si>
+  <si>
+    <t>2.5br_total_agreement_price</t>
+  </si>
+  <si>
+    <t>2br_total_agreement_price</t>
+  </si>
+  <si>
+    <t>3br_total_agreement_price</t>
+  </si>
+  <si>
+    <t>4br_total_agreement_price</t>
+  </si>
+  <si>
+    <t>&gt;3br_total_agreement_price</t>
+  </si>
+  <si>
+    <t>1.5br_avg_agreement_price</t>
+  </si>
+  <si>
+    <t>1br_avg_agreement_price</t>
+  </si>
+  <si>
+    <t>2.5br_avg_agreement_price</t>
+  </si>
+  <si>
+    <t>2br_avg_agreement_price</t>
+  </si>
+  <si>
+    <t>3br_avg_agreement_price</t>
+  </si>
+  <si>
+    <t>4br_avg_agreement_price</t>
+  </si>
+  <si>
+    <t>&gt;3br_avg_agreement_price</t>
+  </si>
+  <si>
+    <t>1.5br_ca_consumed_sqft_igr</t>
+  </si>
+  <si>
+    <t>1br_ca_consumed_sqft_igr</t>
+  </si>
+  <si>
+    <t>2.5br_ca_consumed_sqft_igr</t>
+  </si>
+  <si>
+    <t>2br_ca_consumed_sqft_igr</t>
+  </si>
+  <si>
+    <t>3br_ca_consumed_sqft_igr</t>
+  </si>
+  <si>
+    <t>4br_ca_consumed_sqft_igr</t>
+  </si>
+  <si>
+    <t>&gt;3br_ca_consumed_sqft_igr</t>
   </si>
   <si>
     <t>apartment_transactions_sale</t>
@@ -208,9 +220,15 @@
     <t>warehouse_transactions_sale</t>
   </si>
   <si>
+    <t>gifts_transactions</t>
+  </si>
+  <si>
     <t>lease_transactions</t>
   </si>
   <si>
+    <t>mortgages_transactions</t>
+  </si>
+  <si>
     <t>other_transactions</t>
   </si>
   <si>
@@ -349,76 +367,88 @@
     <t>shop_total_unit_sold_in_rate_range</t>
   </si>
   <si>
-    <t>1.5bhk - wt_avg_rate_nca</t>
-  </si>
-  <si>
-    <t>1bhk - wt_avg_rate_nca</t>
-  </si>
-  <si>
-    <t>2.5bhk - wt_avg_rate_nca</t>
-  </si>
-  <si>
-    <t>2bhk - wt_avg_rate_nca</t>
-  </si>
-  <si>
-    <t>3bhk - wt_avg_rate_nca</t>
-  </si>
-  <si>
-    <t>&gt;3bhk - wt_avg_rate_nca</t>
-  </si>
-  <si>
-    <t>1.5bhk - p50_rate_nca</t>
-  </si>
-  <si>
-    <t>1bhk - p50_rate_nca</t>
-  </si>
-  <si>
-    <t>2.5bhk - p50_rate_nca</t>
-  </si>
-  <si>
-    <t>2bhk - p50_rate_nca</t>
-  </si>
-  <si>
-    <t>3bhk - p50_rate_nca</t>
-  </si>
-  <si>
-    <t>&gt;3bhk - p50_rate_nca</t>
-  </si>
-  <si>
-    <t>1.5bhk - p75_rate_nca</t>
-  </si>
-  <si>
-    <t>1bhk - p75_rate_nca</t>
-  </si>
-  <si>
-    <t>2.5bhk - p75_rate_nca</t>
-  </si>
-  <si>
-    <t>2bhk - p75_rate_nca</t>
-  </si>
-  <si>
-    <t>3bhk - p75_rate_nca</t>
-  </si>
-  <si>
-    <t>&gt;3bhk - p75_rate_nca</t>
-  </si>
-  <si>
-    <t>1.5bhk - p90_rate_nca</t>
-  </si>
-  <si>
-    <t>1bhk - p90_rate_nca</t>
-  </si>
-  <si>
-    <t>2.5bhk - p90_rate_nca</t>
-  </si>
-  <si>
-    <t>2bhk - p90_rate_nca</t>
-  </si>
-  <si>
-    <t>3bhk - p90_rate_nca</t>
-  </si>
-  <si>
-    <t>&gt;3bhk - p90_rate_nca</t>
+    <t>1.5br - wt_avg_rate_nca</t>
+  </si>
+  <si>
+    <t>1br - wt_avg_rate_nca</t>
+  </si>
+  <si>
+    <t>2.5br - wt_avg_rate_nca</t>
+  </si>
+  <si>
+    <t>2br - wt_avg_rate_nca</t>
+  </si>
+  <si>
+    <t>3br - wt_avg_rate_nca</t>
+  </si>
+  <si>
+    <t>4br - wt_avg_rate_nca</t>
+  </si>
+  <si>
+    <t>&gt;3br - wt_avg_rate_nca</t>
+  </si>
+  <si>
+    <t>1.5br - p50_rate_nca</t>
+  </si>
+  <si>
+    <t>1br - p50_rate_nca</t>
+  </si>
+  <si>
+    <t>2.5br - p50_rate_nca</t>
+  </si>
+  <si>
+    <t>2br - p50_rate_nca</t>
+  </si>
+  <si>
+    <t>3br - p50_rate_nca</t>
+  </si>
+  <si>
+    <t>4br - p50_rate_nca</t>
+  </si>
+  <si>
+    <t>&gt;3br - p50_rate_nca</t>
+  </si>
+  <si>
+    <t>1.5br - p75_rate_nca</t>
+  </si>
+  <si>
+    <t>1br - p75_rate_nca</t>
+  </si>
+  <si>
+    <t>2.5br - p75_rate_nca</t>
+  </si>
+  <si>
+    <t>2br - p75_rate_nca</t>
+  </si>
+  <si>
+    <t>3br - p75_rate_nca</t>
+  </si>
+  <si>
+    <t>4br - p75_rate_nca</t>
+  </si>
+  <si>
+    <t>&gt;3br - p75_rate_nca</t>
+  </si>
+  <si>
+    <t>1.5br - p90_rate_nca</t>
+  </si>
+  <si>
+    <t>1br - p90_rate_nca</t>
+  </si>
+  <si>
+    <t>2.5br - p90_rate_nca</t>
+  </si>
+  <si>
+    <t>2br - p90_rate_nca</t>
+  </si>
+  <si>
+    <t>3br - p90_rate_nca</t>
+  </si>
+  <si>
+    <t>4br - p90_rate_nca</t>
+  </si>
+  <si>
+    <t>&gt;3br - p90_rate_nca</t>
   </si>
   <si>
     <t>flat_total_unit_sold_in_area_range</t>
@@ -469,94 +499,109 @@
     <t>shop_avg_agreement_price_in_area_range</t>
   </si>
   <si>
-    <t>1.5bhk_total_unit_sold_in_area_range</t>
-  </si>
-  <si>
-    <t>1bhk_total_unit_sold_in_area_range</t>
-  </si>
-  <si>
-    <t>2.5bhk_total_unit_sold_in_area_range</t>
-  </si>
-  <si>
-    <t>2bhk_total_unit_sold_in_area_range</t>
-  </si>
-  <si>
-    <t>3bhk_total_unit_sold_in_area_range</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_total_unit_sold_in_area_range</t>
-  </si>
-  <si>
-    <t>1.5bhk_total_ca_consumed_in_area_range_sqft</t>
-  </si>
-  <si>
-    <t>1bhk_total_ca_consumed_in_area_range_sqft</t>
-  </si>
-  <si>
-    <t>2.5bhk_total_ca_consumed_in_area_range_sqft</t>
-  </si>
-  <si>
-    <t>2bhk_total_ca_consumed_in_area_range_sqft</t>
-  </si>
-  <si>
-    <t>3bhk_total_ca_consumed_in_area_range_sqft</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_total_ca_consumed_in_area_range_sqft</t>
-  </si>
-  <si>
-    <t>1.5bhk_total_agreement_price_in_area_range</t>
-  </si>
-  <si>
-    <t>1bhk_total_agreement_price_in_area_range</t>
-  </si>
-  <si>
-    <t>2.5bhk_total_agreement_price_in_area_range</t>
-  </si>
-  <si>
-    <t>2bhk_total_agreement_price_in_area_range</t>
-  </si>
-  <si>
-    <t>3bhk_total_agreement_price_in_area_range</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_total_agreement_price_in_area_range</t>
-  </si>
-  <si>
-    <t>1.5bhk_avg_agreement_price_in_area_range</t>
-  </si>
-  <si>
-    <t>1bhk_avg_agreement_price_in_area_range</t>
-  </si>
-  <si>
-    <t>2.5bhk_avg_agreement_price_in_area_range</t>
-  </si>
-  <si>
-    <t>2bhk_avg_agreement_price_in_area_range</t>
-  </si>
-  <si>
-    <t>3bhk_avg_agreement_price_in_area_range</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_avg_agreement_price_in_area_range</t>
-  </si>
-  <si>
-    <t>1.5bhk_avg_carpet_area_in_sqft</t>
-  </si>
-  <si>
-    <t>1bhk_avg_carpet_area_in_sqft</t>
-  </si>
-  <si>
-    <t>2.5bhk_avg_carpet_area_in_sqft</t>
-  </si>
-  <si>
-    <t>2bhk_avg_carpet_area_in_sqft</t>
-  </si>
-  <si>
-    <t>3bhk_avg_carpet_area_in_sqft</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_avg_carpet_area_in_sqft</t>
+    <t>1.5br_total_unit_sold_in_area_range</t>
+  </si>
+  <si>
+    <t>1br_total_unit_sold_in_area_range</t>
+  </si>
+  <si>
+    <t>2.5br_total_unit_sold_in_area_range</t>
+  </si>
+  <si>
+    <t>2br_total_unit_sold_in_area_range</t>
+  </si>
+  <si>
+    <t>3br_total_unit_sold_in_area_range</t>
+  </si>
+  <si>
+    <t>4br_total_unit_sold_in_area_range</t>
+  </si>
+  <si>
+    <t>&gt;3br_total_unit_sold_in_area_range</t>
+  </si>
+  <si>
+    <t>1.5br_total_ca_consumed_in_area_range_sqft</t>
+  </si>
+  <si>
+    <t>1br_total_ca_consumed_in_area_range_sqft</t>
+  </si>
+  <si>
+    <t>2.5br_total_ca_consumed_in_area_range_sqft</t>
+  </si>
+  <si>
+    <t>2br_total_ca_consumed_in_area_range_sqft</t>
+  </si>
+  <si>
+    <t>3br_total_ca_consumed_in_area_range_sqft</t>
+  </si>
+  <si>
+    <t>4br_total_ca_consumed_in_area_range_sqft</t>
+  </si>
+  <si>
+    <t>&gt;3br_total_ca_consumed_in_area_range_sqft</t>
+  </si>
+  <si>
+    <t>1.5br_total_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>1br_total_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>2.5br_total_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>2br_total_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>3br_total_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>4br_total_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>&gt;3br_total_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>1.5br_avg_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>1br_avg_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>2.5br_avg_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>2br_avg_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>3br_avg_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>4br_avg_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>&gt;3br_avg_agreement_price_in_area_range</t>
+  </si>
+  <si>
+    <t>1.5br_avg_carpet_area_in_sqft</t>
+  </si>
+  <si>
+    <t>1br_avg_carpet_area_in_sqft</t>
+  </si>
+  <si>
+    <t>2.5br_avg_carpet_area_in_sqft</t>
+  </si>
+  <si>
+    <t>2br_avg_carpet_area_in_sqft</t>
+  </si>
+  <si>
+    <t>3br_avg_carpet_area_in_sqft</t>
+  </si>
+  <si>
+    <t>4br_avg_carpet_area_in_sqft</t>
+  </si>
+  <si>
+    <t>&gt;3br_avg_carpet_area_in_sqft</t>
   </si>
   <si>
     <t>flat_agreement_price_range_unit_sold</t>
@@ -595,58 +640,67 @@
     <t>shop_agreement_price_range_ca_consumed_sqft</t>
   </si>
   <si>
-    <t>1.5bhk_agreement_price_range_unit_sold</t>
-  </si>
-  <si>
-    <t>1.5bhk_agreement_price_range_total_sales</t>
-  </si>
-  <si>
-    <t>1.5bhk_agreement_price_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>1bhk_agreement_price_range_unit_sold</t>
-  </si>
-  <si>
-    <t>1bhk_agreement_price_range_total_sales</t>
-  </si>
-  <si>
-    <t>1bhk_agreement_price_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>2.5bhk_agreement_price_range_unit_sold</t>
-  </si>
-  <si>
-    <t>2.5bhk_agreement_price_range_total_sales</t>
-  </si>
-  <si>
-    <t>2.5bhk_agreement_price_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>2bhk_agreement_price_range_unit_sold</t>
-  </si>
-  <si>
-    <t>2bhk_agreement_price_range_total_sales</t>
-  </si>
-  <si>
-    <t>2bhk_agreement_price_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>3bhk_agreement_price_range_unit_sold</t>
-  </si>
-  <si>
-    <t>3bhk_agreement_price_range_total_sales</t>
-  </si>
-  <si>
-    <t>3bhk_agreement_price_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_agreement_price_range_unit_sold</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_agreement_price_range_total_sales</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_agreement_price_range_ca_consumed_sqft</t>
+    <t>1br_agreement_price_range_unit_sold</t>
+  </si>
+  <si>
+    <t>1br_agreement_price_range_total_sales</t>
+  </si>
+  <si>
+    <t>1br_agreement_price_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>2br_agreement_price_range_unit_sold</t>
+  </si>
+  <si>
+    <t>2br_agreement_price_range_total_sales</t>
+  </si>
+  <si>
+    <t>2br_agreement_price_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>3br_agreement_price_range_unit_sold</t>
+  </si>
+  <si>
+    <t>3br_agreement_price_range_total_sales</t>
+  </si>
+  <si>
+    <t>3br_agreement_price_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>4br_agreement_price_range_unit_sold</t>
+  </si>
+  <si>
+    <t>4br_agreement_price_range_total_sales</t>
+  </si>
+  <si>
+    <t>4br_agreement_price_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>1.5br_agreement_price_range_unit_sold</t>
+  </si>
+  <si>
+    <t>1.5br_agreement_price_range_total_sales</t>
+  </si>
+  <si>
+    <t>1.5br_agreement_price_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>2.5br_agreement_price_range_unit_sold</t>
+  </si>
+  <si>
+    <t>2.5br_agreement_price_range_total_sales</t>
+  </si>
+  <si>
+    <t>2.5br_agreement_price_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>&gt;3br_agreement_price_range_unit_sold</t>
+  </si>
+  <si>
+    <t>&gt;3br_agreement_price_range_total_sales</t>
+  </si>
+  <si>
+    <t>&gt;3br_agreement_price_range_ca_consumed_sqft</t>
   </si>
   <si>
     <t>flat_rate_range_unit_sold</t>
@@ -685,58 +739,67 @@
     <t>shop_rate_range_ca_consumed_sqft</t>
   </si>
   <si>
-    <t>1.5bhk_rate_range_unit_sold</t>
-  </si>
-  <si>
-    <t>1.5bhk_rate_range_total_sales</t>
-  </si>
-  <si>
-    <t>1.5bhk_rate_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>1bhk_rate_range_unit_sold</t>
-  </si>
-  <si>
-    <t>1bhk_rate_range_total_sales</t>
-  </si>
-  <si>
-    <t>1bhk_rate_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>2.5bhk_rate_range_unit_sold</t>
-  </si>
-  <si>
-    <t>2.5bhk_rate_range_total_sales</t>
-  </si>
-  <si>
-    <t>2.5bhk_rate_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>2bhk_rate_range_unit_sold</t>
-  </si>
-  <si>
-    <t>2bhk_rate_range_total_sales</t>
-  </si>
-  <si>
-    <t>2bhk_rate_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>3bhk_rate_range_unit_sold</t>
-  </si>
-  <si>
-    <t>3bhk_rate_range_total_sales</t>
-  </si>
-  <si>
-    <t>3bhk_rate_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_rate_range_unit_sold</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_rate_range_total_sales</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_rate_range_ca_consumed_sqft</t>
+    <t>1br_rate_range_unit_sold</t>
+  </si>
+  <si>
+    <t>1br_rate_range_total_sales</t>
+  </si>
+  <si>
+    <t>1br_rate_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>2br_rate_range_unit_sold</t>
+  </si>
+  <si>
+    <t>2br_rate_range_total_sales</t>
+  </si>
+  <si>
+    <t>2br_rate_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>3br_rate_range_unit_sold</t>
+  </si>
+  <si>
+    <t>3br_rate_range_total_sales</t>
+  </si>
+  <si>
+    <t>3br_rate_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>4br_rate_range_unit_sold</t>
+  </si>
+  <si>
+    <t>4br_rate_range_total_sales</t>
+  </si>
+  <si>
+    <t>4br_rate_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>1.5br_rate_range_unit_sold</t>
+  </si>
+  <si>
+    <t>1.5br_rate_range_total_sales</t>
+  </si>
+  <si>
+    <t>1.5br_rate_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>2.5br_rate_range_unit_sold</t>
+  </si>
+  <si>
+    <t>2.5br_rate_range_total_sales</t>
+  </si>
+  <si>
+    <t>2.5br_rate_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>&gt;3br_rate_range_unit_sold</t>
+  </si>
+  <si>
+    <t>&gt;3br_rate_range_total_sales</t>
+  </si>
+  <si>
+    <t>&gt;3br_rate_range_ca_consumed_sqft</t>
   </si>
   <si>
     <t>pincode_stats</t>
@@ -778,58 +841,61 @@
     <t>shop_age_range_ca_consumed_sqft</t>
   </si>
   <si>
-    <t>1.5bhk_age_range_unit_sold</t>
-  </si>
-  <si>
-    <t>1.5bhk_age_range_total_agreement_price</t>
-  </si>
-  <si>
-    <t>1.5bhk_age_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>1bhk_age_range_unit_sold</t>
-  </si>
-  <si>
-    <t>1bhk_age_range_total_agreement_price</t>
-  </si>
-  <si>
-    <t>1bhk_age_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>2.5bhk_age_range_unit_sold</t>
-  </si>
-  <si>
-    <t>2.5bhk_age_range_total_agreement_price</t>
-  </si>
-  <si>
-    <t>2.5bhk_age_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>2bhk_age_range_unit_sold</t>
-  </si>
-  <si>
-    <t>2bhk_age_range_total_agreement_price</t>
-  </si>
-  <si>
-    <t>2bhk_age_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>3bhk_age_range_unit_sold</t>
-  </si>
-  <si>
-    <t>3bhk_age_range_total_agreement_price</t>
-  </si>
-  <si>
-    <t>3bhk_age_range_ca_consumed_sqft</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_age_range_unit_sold</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_age_range_total_agreement_price</t>
-  </si>
-  <si>
-    <t>&gt;3bhk_age_range_ca_consumed_sqft</t>
+    <t>1.5br_age_range_unit_sold</t>
+  </si>
+  <si>
+    <t>1.5br_age_range_total_agreement_price</t>
+  </si>
+  <si>
+    <t>1.5br_age_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>1br_age_range_unit_sold</t>
+  </si>
+  <si>
+    <t>1br_age_range_total_agreement_price</t>
+  </si>
+  <si>
+    <t>1br_age_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>2.5br_age_range_unit_sold</t>
+  </si>
+  <si>
+    <t>2.5br_age_range_total_agreement_price</t>
+  </si>
+  <si>
+    <t>2.5br_age_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>2br_age_range_unit_sold</t>
+  </si>
+  <si>
+    <t>2br_age_range_total_agreement_price</t>
+  </si>
+  <si>
+    <t>2br_age_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>3br_age_range_unit_sold</t>
+  </si>
+  <si>
+    <t>3br_age_range_total_agreement_price</t>
+  </si>
+  <si>
+    <t>3br_age_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>&gt;3br_age_range_unit_sold</t>
+  </si>
+  <si>
+    <t>&gt;3br_age_range_total_agreement_price</t>
+  </si>
+  <si>
+    <t>&gt;3br_age_range_ca_consumed_sqft</t>
+  </si>
+  <si>
+    <t>Dubai</t>
   </si>
   <si>
     <t>Pune</t>
@@ -844,15 +910,15 @@
     <t>Residential + Commercial</t>
   </si>
   <si>
+    <t>{}</t>
+  </si>
+  <si>
     <t>{'0-5': 9991.88, '5-10': 10231.2, '10-15': 10548.61, '15-20': 11344.27, '20-25': 11195.61, '25-30': 10826.2, '30-35': 11656.14}</t>
   </si>
   <si>
     <t>{'0-5': 17177.25, '5-10': 21010.92, '10-15': 22385.39, '15-20': 26238.9, '20-25': 23103.88, '25-30': 25373.26, '30-35': 27554.46, '35-40': 27540.0}</t>
   </si>
   <si>
-    <t>{}</t>
-  </si>
-  <si>
     <t>{'0-5': 16735.87, '5-10': 15870.03, '10-15': 11731.9}</t>
   </si>
   <si>
@@ -871,6 +937,9 @@
     <t>{'0-5': 28864.96, '5-10': 5087.51, '10-15': 7146.33, '15-20': 1281.76, '20-25': 5071.34}</t>
   </si>
   <si>
+    <t>2514-3073</t>
+  </si>
+  <si>
     <t>8514-10406</t>
   </si>
   <si>
@@ -880,6 +949,9 @@
     <t>2307-2820</t>
   </si>
   <si>
+    <t>2014-2462</t>
+  </si>
+  <si>
     <t>12496-15273</t>
   </si>
   <si>
@@ -907,6 +979,9 @@
     <t>398-487</t>
   </si>
   <si>
+    <t>{'&lt;2000': 521, '2000-3000': 149, '3000-4000': 72}</t>
+  </si>
+  <si>
     <t>{'7000-8000': 4699, '8000-9000': 4639, '9000-10000': 2720, '6000-7000': 1519, '10000-11000': 1380, '5000-6000': 873, '11000-12000': 654, '4000-5000': 637, '3000-4000': 291, '12000-13000': 230, '&lt;2000': 152, '13000-14000': 57, '2000-3000': 38, '15000-16000': 29, '14000-15000': 19, '&gt;40000': 16, '16000-17000': 13, '17000-18000': 10, '19000-20000': 4, '18000-19000': 4, '25000-26000': 1, '39000-40000': 1, '30000-31000': 1, '21000-22000': 1, '24000-25000': 1, '20000-21000': 1}</t>
   </si>
   <si>
@@ -916,6 +991,9 @@
     <t>{'2000-3000': 8, '3000-4000': 1}</t>
   </si>
   <si>
+    <t>{'&lt;2000': 10, '2000-3000': 4}</t>
+  </si>
+  <si>
     <t>{'13000-14000': 64, '11000-12000': 57, '8000-9000': 53, '12000-13000': 52, '9000-10000': 51, '7000-8000': 47, '10000-11000': 39, '6000-7000': 30, '14000-15000': 22, '5000-6000': 22, '16000-17000': 20, '15000-16000': 15, '4000-5000': 14, '19000-20000': 13, '17000-18000': 11, '3000-4000': 9, '18000-19000': 5, '20000-21000': 4, '&lt;2000': 3, '&gt;40000': 3, '23000-24000': 2, '24000-25000': 2, '2000-3000': 1, '22000-23000': 1, '32000-33000': 1, '21000-22000': 1}</t>
   </si>
   <si>
@@ -943,6 +1021,9 @@
     <t>{'&lt;2000': 9}</t>
   </si>
   <si>
+    <t>{'600-800': 311, '800-1000': 147, '1200-1400': 89, '1400-1600': 78, '1000-1200': 39, '400-600': 28, '1600-1800': 22, '2000-2200': 13, '1800-2000': 11, '3400-3600': 1, '2400-2600': 1, '2800-3000': 1, '3600-3800': 1}</t>
+  </si>
+  <si>
     <t>{'400-600': 6960, '600-800': 6578, '800-1000': 2511, '200-400': 1267, '1000-1200': 580, '1200-1400': 207, '1400-1600': 99, '1600-1800': 32, '1800-2000': 22, '2600-2800': 5, '5200-5400': 4, '2400-2600': 4, '2800-3000': 3, '5600-5800': 3, '3800-4000': 3, '4800-5000': 2, '3000-3200': 2, '2200-2400': 2, '3600-3800': 2, '5400-5600': 2, '2000-2200': 2, '4600-4800': 2, '5000-5200': 1, '3200-3400': 1, '4200-4400': 1, '4000-4200': 1, '6000-6200': 1}</t>
   </si>
   <si>
@@ -952,6 +1033,9 @@
     <t>{'400-600': 9}</t>
   </si>
   <si>
+    <t>{'3200-3400': 14}</t>
+  </si>
+  <si>
     <t>{'200-400': 314, '400-600': 66, '600-800': 38, '800-1000': 4, '2000-2200': 4, '1000-1200': 2, '3400-3600': 2, '1800-2000': 2, '3000-3200': 1, '4000-4200': 1, '4800-5000': 1, '4600-4800': 1, '1600-1800': 1, '1400-1600': 1, '1200-1400': 1}</t>
   </si>
   <si>
@@ -979,6 +1063,9 @@
     <t>{'1800-2000': 2, '2400-2600': 2, '2000-2200': 1, '800-1000': 1, '1000-1200': 1, '1600-1800': 1, '2200-2400': 1}</t>
   </si>
   <si>
+    <t>{'400-600': 14408.69, '600-800': 235515.89, '800-1000': 129716.53, '1000-1200': 44446.06, '1200-1400': 116713.84, '1400-1600': 118217.03, '1600-1800': 36284.69, '1800-2000': 20529.42, '2000-2200': 26634.66, '2400-2600': 2591.22, '2800-3000': 2881.63, '3400-3600': 3492.81, '3600-3800': 3731.66}</t>
+  </si>
+  <si>
     <t>{'200-400': 450937.65, '400-600': 3594969.33, '600-800': 4430922.02, '800-1000': 2235566.76, '1000-1200': 622105.55, '1200-1400': 267340.52, '1400-1600': 148469.2, '1600-1800': 53806.01, '1800-2000': 41389.3, '2000-2200': 4326.37, '2200-2400': 4488.27, '2400-2600': 9871.66, '2600-2800': 13498.06, '2800-3000': 8668.14, '3000-3200': 6197.91, '3200-3400': 3390.66, '3600-3800': 7437.92, '3800-4000': 11504.02, '4000-4200': 4197.96, '4200-4400': 4219.49, '4600-4800': 9515.38, '4800-5000': 9676.41, '5000-5200': 5032.17, '5200-5400': 21528.0, '5400-5600': 11073.57, '5600-5800': 17021.11, '6000-6200': 6060.13}</t>
   </si>
   <si>
@@ -988,6 +1075,9 @@
     <t>{'400-600': 5265.21}</t>
   </si>
   <si>
+    <t>{'3200-3400': 47223.61}</t>
+  </si>
+  <si>
     <t>{'200-400': 95794.11, '400-600': 31579.85, '600-800': 26925.07, '800-1000': 3540.71, '1000-1200': 2281.43, '1200-1400': 1297.71, '1400-1600': 1557.01, '1600-1800': 1634.73, '1800-2000': 3640.38, '2000-2200': 8626.59, '3000-3200': 3126.73, '3400-3600': 7121.46, '4000-4200': 4119.81, '4600-4800': 4761.99, '4800-5000': 4974.26}</t>
   </si>
   <si>
@@ -1015,6 +1105,9 @@
     <t>{'800-1000': 923.98, '1000-1200': 1061.98, '1600-1800': 1701.03, '1800-2000': 3600.13, '2000-2200': 2164.53, '2200-2400': 2236.54, '2400-2600': 5130.12}</t>
   </si>
   <si>
+    <t>{'400-600': 11575527.0, '600-800': 419393039.0, '800-1000': 184493491.0, '1000-1200': 119797381.0, '1200-1400': 183993089.0, '1400-1600': 256248474.0, '1600-1800': 94064109.0, '1800-2000': 43695666.0, '2000-2200': 72219120.0, '2400-2600': 3356432.0, '2800-3000': 8043294.0, '3400-3600': 4394262.0, '3600-3800': 4562107.0}</t>
+  </si>
+  <si>
     <t>{'200-400': 3772639823.0, '400-600': 27443659075.0, '600-800': 35935080970.0, '800-1000': 18249518870.0, '1000-1200': 5358017537.0, '1200-1400': 2265520609.0, '1400-1600': 1302195478.0, '1600-1800': 392493707.0, '1800-2000': 249005000.0, '2000-2200': 20800000.0, '2400-2600': 22432544.0, '2600-2800': 15166851.0, '2800-3000': 8470000.0, '3000-3200': 1625000.0, '3600-3800': 757020.0, '4000-4200': 4000000.0, '4600-4800': 7200000.0, '4800-5000': 7411500.0, '5200-5400': 82200000.0, '5400-5600': 92218104.0, '5600-5800': 5650000.0, '6000-6200': 3300000.0}</t>
   </si>
   <si>
@@ -1024,6 +1117,9 @@
     <t>{'400-600': 14000000.0}</t>
   </si>
   <si>
+    <t>{'3200-3400': 81451588.0}</t>
+  </si>
+  <si>
     <t>{'200-400': 1080458574.0, '400-600': 390731986.0, '600-800': 324324334.0, '800-1000': 41184190.0, '1000-1200': 15713043.0, '1200-1400': 18518541.0, '1400-1600': 20000000.0, '1600-1800': 7800000.0, '1800-2000': 20800000.0, '2000-2200': 48993000.0, '3000-3200': 19500000.0, '3400-3600': 83300000.0, '4000-4200': 28840000.0, '4800-5000': 41800000.0}</t>
   </si>
   <si>
@@ -1051,6 +1147,9 @@
     <t>{'800-1000': 319000.0, '1000-1200': 366000.0, '1600-1800': 586000.0, '1800-2000': 1324000.0, '2000-2200': 1127000.0, '2200-2400': 1725000.0, '2400-2600': 742000.0}</t>
   </si>
   <si>
+    <t>{'400-600': 413411.68, '600-800': 1348530.67, '800-1000': 1255057.76, '1000-1200': 3071727.72, '1200-1400': 2067338.08, '1400-1600': 3285236.85, '1600-1800': 4275641.32, '1800-2000': 3972333.27, '2000-2200': 5555316.92, '2400-2600': 3356432.0, '2800-3000': 8043294.0, '3400-3600': 4394262.0, '3600-3800': 4562107.0}</t>
+  </si>
+  <si>
     <t>{'200-400': 3008484.71, '400-600': 4107102.53, '600-800': 5510670.29, '800-1000': 7288146.51, '1000-1200': 9269926.53, '1200-1400': 11105493.18, '1400-1600': 13153489.68, '1600-1800': 12661087.32, '1800-2000': 11857380.95, '2000-2200': 10400000.0, '2400-2600': 7477514.67, '2600-2800': 3791712.75, '2800-3000': 4235000.0, '3000-3200': 1625000.0, '3600-3800': 757020.0, '4000-4200': 4000000.0, '4600-4800': 3600000.0, '4800-5000': 7411500.0, '5200-5400': 41100000.0, '5400-5600': 92218104.0, '5600-5800': 2825000.0, '6000-6200': 3300000.0}</t>
   </si>
   <si>
@@ -1060,6 +1159,9 @@
     <t>{'400-600': 1555555.56}</t>
   </si>
   <si>
+    <t>{'3200-3400': 5817970.57}</t>
+  </si>
+  <si>
     <t>{'200-400': 3451944.33, '400-600': 5920181.61, '600-800': 8534850.89, '800-1000': 10296047.5, '1000-1200': 7856521.5, '1200-1400': 18518541.0, '1400-1600': 20000000.0, '1600-1800': 7800000.0, '1800-2000': 10400000.0, '2000-2200': 12248250.0, '3000-3200': 19500000.0, '3400-3600': 41650000.0, '4000-4200': 28840000.0, '4800-5000': 41800000.0}</t>
   </si>
   <si>
@@ -1090,6 +1192,9 @@
     <t>{'400-600': 1}</t>
   </si>
   <si>
+    <t>{'600-800': 311, '800-1000': 140, '400-600': 15, '1400-1600': 4}</t>
+  </si>
+  <si>
     <t>{'400-600': 1891, '200-400': 1141, '600-800': 17}</t>
   </si>
   <si>
@@ -1099,18 +1204,27 @@
     <t>{'800-1000': 29, '600-800': 25}</t>
   </si>
   <si>
+    <t>{'1200-1400': 89, '1400-1600': 74, '1000-1200': 39, '1600-1800': 16, '800-1000': 7, '1800-2000': 4}</t>
+  </si>
+  <si>
     <t>{'600-800': 5578, '400-600': 5016, '800-1000': 281, '200-400': 44}</t>
   </si>
   <si>
     <t>{'400-600': 970, '600-800': 274, '200-400': 5, '800-1000': 1}</t>
   </si>
   <si>
+    <t>{'2000-2200': 13, '1800-2000': 7, '1600-1800': 6, '2800-3000': 1, '2400-2600': 1}</t>
+  </si>
+  <si>
     <t>{'800-1000': 2168, '600-800': 954, '1000-1200': 570, '1200-1400': 127, '400-600': 51}</t>
   </si>
   <si>
     <t>{'600-800': 364, '800-1000': 227, '1000-1200': 100, '1200-1400': 4}</t>
   </si>
   <si>
+    <t>{'3600-3800': 1, '3400-3600': 1}</t>
+  </si>
+  <si>
     <t>{'1400-1600': 49, '1200-1400': 35, '800-1000': 33, '1000-1200': 10}</t>
   </si>
   <si>
@@ -1123,6 +1237,9 @@
     <t>{'400-600': 402.25}</t>
   </si>
   <si>
+    <t>{'400-600': 8423.69, '600-800': 235515.89, '800-1000': 122754.38, '1400-1600': 6091.89}</t>
+  </si>
+  <si>
     <t>{'200-400': 413193.79, '400-600': 856402.78, '600-800': 10757.76}</t>
   </si>
   <si>
@@ -1132,18 +1249,27 @@
     <t>{'600-800': 18979.19, '800-1000': 23449.16}</t>
   </si>
   <si>
+    <t>{'800-1000': 6962.16, '1000-1200': 44446.06, '1200-1400': 116713.84, '1400-1600': 112125.14, '1600-1800': 26043.07, '1800-2000': 7373.12}</t>
+  </si>
+  <si>
     <t>{'200-400': 16811.11, '400-600': 2708610.33, '600-800': 3699051.72, '800-1000': 257933.1}</t>
   </si>
   <si>
     <t>{'200-400': 1936.44, '400-600': 514373.37, '600-800': 176718.94, '800-1000': 811.18}</t>
   </si>
   <si>
+    <t>{'1600-1800': 10241.62, '1800-2000': 13156.3, '2000-2200': 26634.66, '2400-2600': 2591.22, '2800-3000': 2881.63}</t>
+  </si>
+  <si>
     <t>{'400-600': 28915.98, '600-800': 699658.92, '800-1000': 1926110.59, '1000-1200': 611073.53, '1200-1400': 161824.25}</t>
   </si>
   <si>
     <t>{'600-800': 267788.46, '800-1000': 202887.62, '1000-1200': 106899.01, '1200-1400': 5003.54}</t>
   </si>
   <si>
+    <t>{'3400-3600': 3492.81, '3600-3800': 3731.66}</t>
+  </si>
+  <si>
     <t>{'800-1000': 28073.91, '1000-1200': 11032.02, '1200-1400': 44538.96, '1400-1600': 72631.38}</t>
   </si>
   <si>
@@ -1156,6 +1282,9 @@
     <t>{'400-600': 10500000.0}</t>
   </si>
   <si>
+    <t>{'400-600': 6460000.0, '600-800': 419393039.0, '800-1000': 174469251.0, '1400-1600': 7669000.0}</t>
+  </si>
+  <si>
     <t>{'200-400': 3398545727.0, '400-600': 6417796791.0, '600-800': 77055444.0}</t>
   </si>
   <si>
@@ -1165,18 +1294,27 @@
     <t>{'600-800': 151535732.0, '800-1000': 220029486.0}</t>
   </si>
   <si>
+    <t>{'800-1000': 10024240.0, '1000-1200': 119797381.0, '1200-1400': 183993089.0, '1400-1600': 248579474.0, '1600-1800': 66583635.0, '1800-2000': 10324267.0}</t>
+  </si>
+  <si>
     <t>{'200-400': 155701221.0, '400-600': 20723570284.0, '600-800': 29704936884.0, '800-1000': 2202229855.0}</t>
   </si>
   <si>
     <t>{'200-400': 19790000.0, '400-600': 5468467976.0, '600-800': 2133058300.0, '800-1000': 15000000.0}</t>
   </si>
   <si>
+    <t>{'1600-1800': 27480474.0, '1800-2000': 33371399.0, '2000-2200': 72219120.0, '2400-2600': 3356432.0, '2800-3000': 8043294.0}</t>
+  </si>
+  <si>
     <t>{'400-600': 294405000.0, '600-800': 5979661389.0, '800-1000': 15602607070.0, '1000-1200': 5276033459.0, '1200-1400': 1455865718.0}</t>
   </si>
   <si>
     <t>{'600-800': 3303293319.0, '800-1000': 2490475548.0, '1000-1200': 1417538832.0, '1200-1400': 77400000.0}</t>
   </si>
   <si>
+    <t>{'3400-3600': 4394262.0, '3600-3800': 4562107.0}</t>
+  </si>
+  <si>
     <t>{'800-1000': 224652459.0, '1000-1200': 81984078.0, '1200-1400': 401147956.0, '1400-1600': 697708724.0}</t>
   </si>
   <si>
@@ -1186,6 +1324,9 @@
     <t>{'400-600': 3943500.0, '600-800': 5472880.25}</t>
   </si>
   <si>
+    <t>{'400-600': 430666.67, '600-800': 1348530.67, '800-1000': 1246208.94, '1400-1600': 1917250.0}</t>
+  </si>
+  <si>
     <t>{'200-400': 3007562.59, '400-600': 3461594.82, '600-800': 4532673.18}</t>
   </si>
   <si>
@@ -1195,12 +1336,18 @@
     <t>{'600-800': 6061429.28, '800-1000': 7587223.66}</t>
   </si>
   <si>
+    <t>{'800-1000': 1432034.29, '1000-1200': 3071727.72, '1200-1400': 2067338.08, '1400-1600': 3359182.08, '1600-1800': 4161477.19, '1800-2000': 2581066.75}</t>
+  </si>
+  <si>
     <t>{'200-400': 3538664.11, '400-600': 4340014.72, '600-800': 5378406.1, '800-1000': 7837116.92}</t>
   </si>
   <si>
     <t>{'200-400': 3958000.0, '400-600': 5708212.92, '600-800': 7988982.4, '800-1000': 15000000.0}</t>
   </si>
   <si>
+    <t>{'1600-1800': 4580079.0, '1800-2000': 4767342.71, '2000-2200': 5555316.92, '2400-2600': 3356432.0, '2800-3000': 8043294.0}</t>
+  </si>
+  <si>
     <t>{'400-600': 5772647.06, '600-800': 6281156.92, '800-1000': 7220086.57, '1000-1200': 9288791.3, '1200-1400': 11646925.74}</t>
   </si>
   <si>
@@ -1213,6 +1360,9 @@
     <t>{'800-1000': 16100000.0}</t>
   </si>
   <si>
+    <t>{'25.00 L - 45.00 L': 120, '45.00 L - 65.00 L': 48, '5.00 L - 25.00 L': 516, '65.00 L - 85.00 L': 1, '&lt; 5.00 L': 57}</t>
+  </si>
+  <si>
     <t>{'1.05 Cr - 1.25 Cr': 251, '1.25 Cr - 1.45 Cr': 141, '1.45 Cr - 1.65 Cr': 78, '1.65 Cr - 1.85 Cr': 22, '1.85 Cr - 2.05 Cr': 6, '25.00 L - 45.00 L': 7755, '45.00 L - 65.00 L': 5315, '5.00 L - 25.00 L': 908, '65.00 L - 85.00 L': 2741, '85.00 L - 1.05 Cr': 729, '&lt; 5.00 L': 108, '&gt; 2.00 Cr': 16}</t>
   </si>
   <si>
@@ -1222,6 +1372,9 @@
     <t>{'5.00 L - 25.00 L': 9}</t>
   </si>
   <si>
+    <t>{'25.00 L - 45.00 L': 388971861.0, '45.00 L - 65.00 L': 238637256.0, '5.00 L - 25.00 L': 746683177.0, '65.00 L - 85.00 L': 8043294.0, '&lt; 5.00 L': 23500403.0}</t>
+  </si>
+  <si>
     <t>{'1.05 Cr - 1.25 Cr': 2862006587.0, '1.25 Cr - 1.45 Cr': 1882801821.0, '1.45 Cr - 1.65 Cr': 1191847731.0, '1.65 Cr - 1.85 Cr': 377094585.0, '1.85 Cr - 2.05 Cr': 116527565.0, '25.00 L - 45.00 L': 30573405684.0, '45.00 L - 65.00 L': 29442270880.0, '5.00 L - 25.00 L': 1737025415.0, '65.00 L - 85.00 L': 20069621005.0, '85.00 L - 1.05 Cr': 6894646931.0, '&lt; 5.00 L': 16073977.0, '&gt; 2.00 Cr': 1223747704.0}</t>
   </si>
   <si>
@@ -1231,6 +1384,9 @@
     <t>{'5.00 L - 25.00 L': 14000000.0}</t>
   </si>
   <si>
+    <t>{'25.00 L - 45.00 L': 165309.1, '45.00 L - 65.00 L': 86545.57, '5.00 L - 25.00 L': 465451.29, '65.00 L - 85.00 L': 2881.63, '&lt; 5.00 L': 34976.54}</t>
+  </si>
+  <si>
     <t>{'1.05 Cr - 1.25 Cr': 323103.74, '1.25 Cr - 1.45 Cr': 171480.15, '1.45 Cr - 1.65 Cr': 109741.99, '1.65 Cr - 1.85 Cr': 33427.6, '1.85 Cr - 2.05 Cr': 8873.09, '25.00 L - 45.00 L': 4194388.4, '45.00 L - 65.00 L': 3583106.39, '5.00 L - 25.00 L': 446466.07, '65.00 L - 85.00 L': 2235443.62, '85.00 L - 1.05 Cr': 712600.32, '&lt; 5.00 L': 35370.93, '&gt; 2.00 Cr': 136272.13}</t>
   </si>
   <si>
@@ -1240,6 +1396,9 @@
     <t>{'5.00 L - 25.00 L': 5265.21}</t>
   </si>
   <si>
+    <t>{'25.00 L - 45.00 L': 5, '45.00 L - 65.00 L': 4, '65.00 L - 85.00 L': 5}</t>
+  </si>
+  <si>
     <t>{'1.05 Cr - 1.25 Cr': 7, '1.25 Cr - 1.45 Cr': 4, '1.45 Cr - 1.65 Cr': 2, '1.65 Cr - 1.85 Cr': 1, '1.85 Cr - 2.05 Cr': 4, '25.00 L - 45.00 L': 183, '45.00 L - 65.00 L': 103, '5.00 L - 25.00 L': 185, '65.00 L - 85.00 L': 22, '85.00 L - 1.05 Cr': 21, '&lt; 5.00 L': 1, '&gt; 2.00 Cr': 10}</t>
   </si>
   <si>
@@ -1249,6 +1408,9 @@
     <t>{'5.00 L - 25.00 L': 2}</t>
   </si>
   <si>
+    <t>{'25.00 L - 45.00 L': 20176588.0, '45.00 L - 65.00 L': 22875000.0, '65.00 L - 85.00 L': 38400000.0}</t>
+  </si>
+  <si>
     <t>{'1.05 Cr - 1.25 Cr': 81303020.0, '1.25 Cr - 1.45 Cr': 53407190.0, '1.45 Cr - 1.65 Cr': 31621050.0, '1.65 Cr - 1.85 Cr': 17000000.0, '1.85 Cr - 2.05 Cr': 77569165.0, '25.00 L - 45.00 L': 629839195.0, '45.00 L - 65.00 L': 542711152.0, '5.00 L - 25.00 L': 314352594.0, '65.00 L - 85.00 L': 157847064.0, '85.00 L - 1.05 Cr': 196938024.0, '&lt; 5.00 L': 100000.0, '&gt; 2.00 Cr': 447804056.0}</t>
   </si>
   <si>
@@ -1258,6 +1420,9 @@
     <t>{'5.00 L - 25.00 L': 1198000.0}</t>
   </si>
   <si>
+    <t>{'25.00 L - 45.00 L': 16865.57, '45.00 L - 65.00 L': 13492.46, '65.00 L - 85.00 L': 16865.57}</t>
+  </si>
+  <si>
     <t>{'1.05 Cr - 1.25 Cr': 6359.48, '1.25 Cr - 1.45 Cr': 3084.96, '1.45 Cr - 1.65 Cr': 1539.68, '1.65 Cr - 1.85 Cr': 751.65, '1.85 Cr - 2.05 Cr': 6456.79, '25.00 L - 45.00 L': 63437.53, '45.00 L - 65.00 L': 42696.05, '5.00 L - 25.00 L': 39911.19, '65.00 L - 85.00 L': 12275.48, '85.00 L - 1.05 Cr': 14644.1, '&lt; 5.00 L': 164.9, '&gt; 2.00 Cr': 52953.39}</t>
   </si>
   <si>
@@ -1321,6 +1486,96 @@
     <t>{'5.00 L - 25.00 L': 9702.24, '&lt; 5.00 L': 7116.08}</t>
   </si>
   <si>
+    <t>{'25.00 L - 45.00 L': 8, '5.00 L - 25.00 L': 416, '&lt; 5.00 L': 46}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 2348, '45.00 L - 65.00 L': 133, '5.00 L - 25.00 L': 490, '65.00 L - 85.00 L': 19, '&lt; 5.00 L': 11}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 3, '25.00 L - 45.00 L': 267, '45.00 L - 65.00 L': 429, '5.00 L - 25.00 L': 123, '65.00 L - 85.00 L': 180, '85.00 L - 1.05 Cr': 5, '&lt; 5.00 L': 148}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 20454200.0, '5.00 L - 25.00 L': 568129006.0, '&lt; 5.00 L': 19408084.0}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 8116743962.0, '45.00 L - 65.00 L': 693551114.0, '5.00 L - 25.00 L': 944642286.0, '65.00 L - 85.00 L': 135973600.0, '&lt; 5.00 L': 2487000.0}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 33750000.0, '25.00 L - 45.00 L': 1016491051.0, '45.00 L - 65.00 L': 2350650600.0, '5.00 L - 25.00 L': 220672111.0, '65.00 L - 85.00 L': 1314780000.0, '85.00 L - 1.05 Cr': 46600000.0, '&lt; 5.00 L': 2731080.0}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 6200.06, '5.00 L - 25.00 L': 336641.3, '&lt; 5.00 L': 29944.48}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 976986.39, '45.00 L - 65.00 L': 65586.13, '5.00 L - 25.00 L': 204375.96, '65.00 L - 85.00 L': 9292.78, '&lt; 5.00 L': 4353.39}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 1200.29, '25.00 L - 45.00 L': 98625.47, '45.00 L - 65.00 L': 165035.69, '5.00 L - 25.00 L': 43341.08, '65.00 L - 85.00 L': 69652.0, '85.00 L - 1.05 Cr': 1899.52, '&lt; 5.00 L': 56976.59}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 106, '45.00 L - 65.00 L': 25, '5.00 L - 25.00 L': 98}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 13, '1.25 Cr - 1.45 Cr': 1, '1.85 Cr - 2.05 Cr': 1, '25.00 L - 45.00 L': 5109, '45.00 L - 65.00 L': 4038, '5.00 L - 25.00 L': 283, '65.00 L - 85.00 L': 1061, '85.00 L - 1.05 Cr': 97, '&lt; 5.00 L': 20}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 69, '1.25 Cr - 1.45 Cr': 31, '1.45 Cr - 1.65 Cr': 10, '1.65 Cr - 1.85 Cr': 2, '25.00 L - 45.00 L': 138, '45.00 L - 65.00 L': 406, '5.00 L - 25.00 L': 56, '65.00 L - 85.00 L': 282, '85.00 L - 1.05 Cr': 113, '&lt; 5.00 L': 118, '&gt; 2.00 Cr': 6}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 343395313.0, '45.00 L - 65.00 L': 118375810.0, '5.00 L - 25.00 L': 177530963.0}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 144052768.0, '1.25 Cr - 1.45 Cr': 12522000.0, '1.85 Cr - 2.05 Cr': 18792600.0, '25.00 L - 45.00 L': 21322374663.0, '45.00 L - 65.00 L': 22106869464.0, '5.00 L - 25.00 L': 589545816.0, '65.00 L - 85.00 L': 7668747585.0, '85.00 L - 1.05 Cr': 916484172.0, '&lt; 5.00 L': 7049176.0}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 798642000.0, '1.25 Cr - 1.45 Cr': 418046000.0, '1.45 Cr - 1.65 Cr': 150800000.0, '1.65 Cr - 1.85 Cr': 35100000.0, '25.00 L - 45.00 L': 533281400.0, '45.00 L - 65.00 L': 2289350861.0, '5.00 L - 25.00 L': 109731000.0, '65.00 L - 85.00 L': 2102409075.0, '85.00 L - 1.05 Cr': 1063879999.0, '&lt; 5.00 L': 1675941.0, '&gt; 2.00 Cr': 133400000.0}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 146080.18, '45.00 L - 65.00 L': 39726.16, '5.00 L - 25.00 L': 127857.05}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 9978.44, '1.25 Cr - 1.45 Cr': 650.79, '1.85 Cr - 2.05 Cr': 610.32, '25.00 L - 45.00 L': 2905194.34, '45.00 L - 65.00 L': 2579255.15, '5.00 L - 25.00 L': 154640.14, '65.00 L - 85.00 L': 757501.0, '85.00 L - 1.05 Cr': 86156.35, '&lt; 5.00 L': 11780.12}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 42568.71, '1.25 Cr - 1.45 Cr': 18828.17, '1.45 Cr - 1.65 Cr': 6506.19, '1.65 Cr - 1.85 Cr': 1274.57, '25.00 L - 45.00 L': 72790.26, '45.00 L - 65.00 L': 218948.67, '5.00 L - 25.00 L': 29119.42, '65.00 L - 85.00 L': 159842.92, '85.00 L - 1.05 Cr': 64209.63, '&lt; 5.00 L': 65126.76, '&gt; 2.00 Cr': 3863.85}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 5, '45.00 L - 65.00 L': 22, '65.00 L - 85.00 L': 1}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 192, '1.25 Cr - 1.45 Cr': 96, '1.45 Cr - 1.65 Cr': 44, '1.65 Cr - 1.85 Cr': 2, '1.85 Cr - 2.05 Cr': 1, '25.00 L - 45.00 L': 227, '45.00 L - 65.00 L': 1080, '5.00 L - 25.00 L': 50, '65.00 L - 85.00 L': 1561, '85.00 L - 1.05 Cr': 601, '&lt; 5.00 L': 3}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 107, '1.25 Cr - 1.45 Cr': 55, '1.45 Cr - 1.65 Cr': 52, '1.65 Cr - 1.85 Cr': 43, '1.85 Cr - 2.05 Cr': 23, '25.00 L - 45.00 L': 4, '45.00 L - 65.00 L': 43, '5.00 L - 25.00 L': 6, '65.00 L - 85.00 L': 111, '85.00 L - 1.05 Cr': 149, '&lt; 5.00 L': 58, '&gt; 2.00 Cr': 31}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 20728086.0, '45.00 L - 65.00 L': 115699339.0, '65.00 L - 85.00 L': 8043294.0}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 2185086956.0, '1.25 Cr - 1.45 Cr': 1277299321.0, '1.45 Cr - 1.65 Cr': 668058384.0, '1.65 Cr - 1.85 Cr': 34400000.0, '1.85 Cr - 2.05 Cr': 18621601.0, '25.00 L - 45.00 L': 896618730.0, '45.00 L - 65.00 L': 6273952145.0, '5.00 L - 25.00 L': 63581290.0, '65.00 L - 85.00 L': 11509163047.0, '85.00 L - 1.05 Cr': 5681130162.0, '&lt; 5.00 L': 661000.0}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 1224451710.0, '1.25 Cr - 1.45 Cr': 754914179.0, '1.45 Cr - 1.65 Cr': 800733520.0, '1.65 Cr - 1.85 Cr': 752501412.0, '1.85 Cr - 2.05 Cr': 447360086.0, '25.00 L - 45.00 L': 15100000.0, '45.00 L - 65.00 L': 246306500.0, '5.00 L - 25.00 L': 5891418.0, '65.00 L - 85.00 L': 862558000.0, '85.00 L - 1.05 Cr': 1434738001.0, '&lt; 5.00 L': 1486816.0, '&gt; 2.00 Cr': 742666057.0}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 9536.04, '45.00 L - 65.00 L': 43087.75, '65.00 L - 85.00 L': 2881.63}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 205117.92, '1.25 Cr - 1.45 Cr': 105939.07, '1.45 Cr - 1.65 Cr': 54488.34, '1.65 Cr - 1.85 Cr': 1995.0, '1.85 Cr - 2.05 Cr': 969.19, '25.00 L - 45.00 L': 195919.55, '45.00 L - 65.00 L': 875446.52, '5.00 L - 25.00 L': 46040.75, '65.00 L - 85.00 L': 1346306.33, '85.00 L - 1.05 Cr': 580116.42, '&lt; 5.00 L': 2714.14}</t>
+  </si>
+  <si>
+    <t>{'1.05 Cr - 1.25 Cr': 90675.94, '1.25 Cr - 1.45 Cr': 49022.59, '1.45 Cr - 1.65 Cr': 47796.68, '1.65 Cr - 1.85 Cr': 36744.74, '1.85 Cr - 2.05 Cr': 20361.51, '25.00 L - 45.00 L': 2955.47, '45.00 L - 65.00 L': 33493.91, '5.00 L - 25.00 L': 5411.28, '65.00 L - 85.00 L': 87454.8, '85.00 L - 1.05 Cr': 122847.49, '&lt; 5.00 L': 46943.26, '&gt; 2.00 Cr': 29267.21}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 1, '45.00 L - 65.00 L': 1}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 4394262.0, '45.00 L - 65.00 L': 4562107.0}</t>
+  </si>
+  <si>
+    <t>{'25.00 L - 45.00 L': 3492.81, '45.00 L - 65.00 L': 3731.66}</t>
+  </si>
+  <si>
     <t>{'25.00 L - 45.00 L': 2, '45.00 L - 65.00 L': 4}</t>
   </si>
   <si>
@@ -1339,24 +1594,6 @@
     <t>{'85.00 L - 1.05 Cr': 402.25}</t>
   </si>
   <si>
-    <t>{'25.00 L - 45.00 L': 2348, '45.00 L - 65.00 L': 133, '5.00 L - 25.00 L': 490, '65.00 L - 85.00 L': 19, '&lt; 5.00 L': 11}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 3, '25.00 L - 45.00 L': 267, '45.00 L - 65.00 L': 429, '5.00 L - 25.00 L': 123, '65.00 L - 85.00 L': 180, '85.00 L - 1.05 Cr': 5, '&lt; 5.00 L': 148}</t>
-  </si>
-  <si>
-    <t>{'25.00 L - 45.00 L': 8116743962.0, '45.00 L - 65.00 L': 693551114.0, '5.00 L - 25.00 L': 944642286.0, '65.00 L - 85.00 L': 135973600.0, '&lt; 5.00 L': 2487000.0}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 33750000.0, '25.00 L - 45.00 L': 1016491051.0, '45.00 L - 65.00 L': 2350650600.0, '5.00 L - 25.00 L': 220672111.0, '65.00 L - 85.00 L': 1314780000.0, '85.00 L - 1.05 Cr': 46600000.0, '&lt; 5.00 L': 2731080.0}</t>
-  </si>
-  <si>
-    <t>{'25.00 L - 45.00 L': 976986.39, '45.00 L - 65.00 L': 65586.13, '5.00 L - 25.00 L': 204375.96, '65.00 L - 85.00 L': 9292.78, '&lt; 5.00 L': 4353.39}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 1200.29, '25.00 L - 45.00 L': 98625.47, '45.00 L - 65.00 L': 165035.69, '5.00 L - 25.00 L': 43341.08, '65.00 L - 85.00 L': 69652.0, '85.00 L - 1.05 Cr': 1899.52, '&lt; 5.00 L': 56976.59}</t>
-  </si>
-  <si>
     <t>{'45.00 L - 65.00 L': 22, '65.00 L - 85.00 L': 32}</t>
   </si>
   <si>
@@ -1366,42 +1603,6 @@
     <t>{'45.00 L - 65.00 L': 16683.12, '65.00 L - 85.00 L': 25745.23}</t>
   </si>
   <si>
-    <t>{'1.05 Cr - 1.25 Cr': 13, '1.25 Cr - 1.45 Cr': 1, '1.85 Cr - 2.05 Cr': 1, '25.00 L - 45.00 L': 5109, '45.00 L - 65.00 L': 4038, '5.00 L - 25.00 L': 283, '65.00 L - 85.00 L': 1061, '85.00 L - 1.05 Cr': 97, '&lt; 5.00 L': 20}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 69, '1.25 Cr - 1.45 Cr': 31, '1.45 Cr - 1.65 Cr': 10, '1.65 Cr - 1.85 Cr': 2, '25.00 L - 45.00 L': 138, '45.00 L - 65.00 L': 406, '5.00 L - 25.00 L': 56, '65.00 L - 85.00 L': 282, '85.00 L - 1.05 Cr': 113, '&lt; 5.00 L': 118, '&gt; 2.00 Cr': 6}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 144052768.0, '1.25 Cr - 1.45 Cr': 12522000.0, '1.85 Cr - 2.05 Cr': 18792600.0, '25.00 L - 45.00 L': 21322374663.0, '45.00 L - 65.00 L': 22106869464.0, '5.00 L - 25.00 L': 589545816.0, '65.00 L - 85.00 L': 7668747585.0, '85.00 L - 1.05 Cr': 916484172.0, '&lt; 5.00 L': 7049176.0}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 798642000.0, '1.25 Cr - 1.45 Cr': 418046000.0, '1.45 Cr - 1.65 Cr': 150800000.0, '1.65 Cr - 1.85 Cr': 35100000.0, '25.00 L - 45.00 L': 533281400.0, '45.00 L - 65.00 L': 2289350861.0, '5.00 L - 25.00 L': 109731000.0, '65.00 L - 85.00 L': 2102409075.0, '85.00 L - 1.05 Cr': 1063879999.0, '&lt; 5.00 L': 1675941.0, '&gt; 2.00 Cr': 133400000.0}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 9978.44, '1.25 Cr - 1.45 Cr': 650.79, '1.85 Cr - 2.05 Cr': 610.32, '25.00 L - 45.00 L': 2905194.34, '45.00 L - 65.00 L': 2579255.15, '5.00 L - 25.00 L': 154640.14, '65.00 L - 85.00 L': 757501.0, '85.00 L - 1.05 Cr': 86156.35, '&lt; 5.00 L': 11780.12}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 42568.71, '1.25 Cr - 1.45 Cr': 18828.17, '1.45 Cr - 1.65 Cr': 6506.19, '1.65 Cr - 1.85 Cr': 1274.57, '25.00 L - 45.00 L': 72790.26, '45.00 L - 65.00 L': 218948.67, '5.00 L - 25.00 L': 29119.42, '65.00 L - 85.00 L': 159842.92, '85.00 L - 1.05 Cr': 64209.63, '&lt; 5.00 L': 65126.76, '&gt; 2.00 Cr': 3863.85}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 192, '1.25 Cr - 1.45 Cr': 96, '1.45 Cr - 1.65 Cr': 44, '1.65 Cr - 1.85 Cr': 2, '1.85 Cr - 2.05 Cr': 1, '25.00 L - 45.00 L': 227, '45.00 L - 65.00 L': 1080, '5.00 L - 25.00 L': 50, '65.00 L - 85.00 L': 1561, '85.00 L - 1.05 Cr': 601, '&lt; 5.00 L': 3}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 107, '1.25 Cr - 1.45 Cr': 55, '1.45 Cr - 1.65 Cr': 52, '1.65 Cr - 1.85 Cr': 43, '1.85 Cr - 2.05 Cr': 23, '25.00 L - 45.00 L': 4, '45.00 L - 65.00 L': 43, '5.00 L - 25.00 L': 6, '65.00 L - 85.00 L': 111, '85.00 L - 1.05 Cr': 149, '&lt; 5.00 L': 58, '&gt; 2.00 Cr': 31}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 2185086956.0, '1.25 Cr - 1.45 Cr': 1277299321.0, '1.45 Cr - 1.65 Cr': 668058384.0, '1.65 Cr - 1.85 Cr': 34400000.0, '1.85 Cr - 2.05 Cr': 18621601.0, '25.00 L - 45.00 L': 896618730.0, '45.00 L - 65.00 L': 6273952145.0, '5.00 L - 25.00 L': 63581290.0, '65.00 L - 85.00 L': 11509163047.0, '85.00 L - 1.05 Cr': 5681130162.0, '&lt; 5.00 L': 661000.0}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 1224451710.0, '1.25 Cr - 1.45 Cr': 754914179.0, '1.45 Cr - 1.65 Cr': 800733520.0, '1.65 Cr - 1.85 Cr': 752501412.0, '1.85 Cr - 2.05 Cr': 447360086.0, '25.00 L - 45.00 L': 15100000.0, '45.00 L - 65.00 L': 246306500.0, '5.00 L - 25.00 L': 5891418.0, '65.00 L - 85.00 L': 862558000.0, '85.00 L - 1.05 Cr': 1434738001.0, '&lt; 5.00 L': 1486816.0, '&gt; 2.00 Cr': 742666057.0}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 205117.92, '1.25 Cr - 1.45 Cr': 105939.07, '1.45 Cr - 1.65 Cr': 54488.34, '1.65 Cr - 1.85 Cr': 1995.0, '1.85 Cr - 2.05 Cr': 969.19, '25.00 L - 45.00 L': 195919.55, '45.00 L - 65.00 L': 875446.52, '5.00 L - 25.00 L': 46040.75, '65.00 L - 85.00 L': 1346306.33, '85.00 L - 1.05 Cr': 580116.42, '&lt; 5.00 L': 2714.14}</t>
-  </si>
-  <si>
-    <t>{'1.05 Cr - 1.25 Cr': 90675.94, '1.25 Cr - 1.45 Cr': 49022.59, '1.45 Cr - 1.65 Cr': 47796.68, '1.65 Cr - 1.85 Cr': 36744.74, '1.85 Cr - 2.05 Cr': 20361.51, '25.00 L - 45.00 L': 2955.47, '45.00 L - 65.00 L': 33493.91, '5.00 L - 25.00 L': 5411.28, '65.00 L - 85.00 L': 87454.8, '85.00 L - 1.05 Cr': 122847.49, '&lt; 5.00 L': 46943.26, '&gt; 2.00 Cr': 29267.21}</t>
-  </si>
-  <si>
     <t>{'1.05 Cr - 1.25 Cr': 28, '1.25 Cr - 1.45 Cr': 30, '1.45 Cr - 1.65 Cr': 7, '1.65 Cr - 1.85 Cr': 11, '45.00 L - 65.00 L': 11, '65.00 L - 85.00 L': 33, '85.00 L - 1.05 Cr': 7}</t>
   </si>
   <si>
@@ -1426,6 +1627,9 @@
     <t>{'&lt;2000': 533, '2000-3000': 24, '3000-4000': 54, '4000-5000': 73, '5000-6000': 90, '6000-7000': 84, '7000-8000': 111, '8000-9000': 148, '9000-10000': 213, '10000-11000': 254, '11000-12000': 333, '12000-13000': 285, '13000-14000': 278, '14000-15000': 260, '15000-16000': 190, '16000-17000': 149, '17000-18000': 115, '18000-19000': 108, '19000-20000': 120, '20000-21000': 85, '21000-22000': 77, '22000-23000': 63, '23000-24000': 47, '24000-25000': 27, '25000-26000': 27, '26000-27000': 23, '27000-28000': 20, '28000-29000': 7, '29000-30000': 5, '30000-31000': 3, '31000-32000': 4, '33000-34000': 5, '35000-36000': 2, '36000-37000': 1, '37000-38000': 1, '&gt;40000': 4}</t>
   </si>
   <si>
+    <t>{'&lt;2000': 668266505.0, '2000-3000': 518695846.0, '3000-4000': 218873640.0}</t>
+  </si>
+  <si>
     <t>{'&lt;2000': 232841702.0, '2000-3000': 146031449.0, '3000-4000': 593778729.0, '4000-5000': 1875330075.0, '5000-6000': 3429502285.0, '6000-7000': 6985864884.0, '7000-8000': 22777466898.0, '8000-9000': 24817057341.0, '9000-10000': 16537366166.0, '10000-11000': 9931559384.0, '11000-12000': 5186169452.0, '12000-13000': 2020551965.0, '13000-14000': 533569380.0, '14000-15000': 174923425.0, '15000-16000': 227327127.0, '16000-17000': 228357646.0, '17000-18000': 98063056.0, '18000-19000': 41700000.0, '19000-20000': 46780481.0, '20000-21000': 6850000.0, '21000-22000': 7160000.0, '24000-25000': 7000000.0, '25000-26000': 8500000.0, '30000-31000': 18792600.0, '39000-40000': 8100000.0, '&gt;40000': 96835327.0}</t>
   </si>
   <si>
@@ -1435,6 +1639,9 @@
     <t>{'2000-3000': 12000000.0, '3000-4000': 2000000.0}</t>
   </si>
   <si>
+    <t>{'&lt;2000': 488191.21, '2000-3000': 196814.36, '3000-4000': 70158.57}</t>
+  </si>
+  <si>
     <t>{'&lt;2000': 318052.36, '2000-3000': 55835.24, '3000-4000': 165703.81, '4000-5000': 408069.27, '5000-6000': 623053.97, '6000-7000': 1062540.27, '7000-8000': 3017961.88, '8000-9000': 2927573.24, '9000-10000': 1752135.4, '10000-11000': 950188.39, '11000-12000': 453315.63, '12000-13000': 162518.32, '13000-14000': 39776.32, '14000-15000': 12189.58, '15000-16000': 14728.7, '16000-17000': 13755.64, '17000-18000': 5618.92, '18000-19000': 2280.78, '19000-20000': 2434.39, '20000-21000': 334.76, '21000-22000': 340.03, '24000-25000': 283.95, '25000-26000': 331.75, '30000-31000': 610.32, '39000-40000': 206.24, '&gt;40000': 435.3}</t>
   </si>
   <si>
@@ -1450,6 +1657,9 @@
     <t>{'&lt;2000': 1, '5000-6000': 1, '8000-9000': 3, '11000-12000': 1, '12000-13000': 5, '13000-14000': 3, '14000-15000': 1, '15000-16000': 1, '28000-29000': 3, '31000-32000': 3}</t>
   </si>
   <si>
+    <t>{'&lt;2000': 49701588.0, '2000-3000': 31750000.0}</t>
+  </si>
+  <si>
     <t>{'&lt;2000': 6100000.0, '2000-3000': 500000.0, '3000-4000': 37320000.0, '4000-5000': 27389000.0, '5000-6000': 56833000.0, '6000-7000': 88122189.0, '7000-8000': 144277837.0, '8000-9000': 296600246.0, '9000-10000': 254551063.0, '10000-11000': 195175317.0, '11000-12000': 177606710.0, '12000-13000': 277595766.0, '13000-14000': 294901749.0, '14000-15000': 131197428.0, '15000-16000': 98488790.0, '16000-17000': 129514328.0, '17000-18000': 64975000.0, '18000-19000': 37209486.0, '19000-20000': 73394601.0, '20000-21000': 55688505.0, '21000-22000': 7000000.0, '22000-23000': 17000000.0, '23000-24000': 13000000.0, '24000-25000': 15300000.0, '32000-33000': 3010000.0, '&gt;40000': 44541495.0}</t>
   </si>
   <si>
@@ -1459,6 +1669,9 @@
     <t>{'&lt;2000': 1198000.0}</t>
   </si>
   <si>
+    <t>{'&lt;2000': 33731.15, '2000-3000': 13492.46}</t>
+  </si>
+  <si>
     <t>{'&lt;2000': 4556.62, '2000-3000': 227.98, '3000-4000': 11048.28, '4000-5000': 5948.19, '5000-6000': 10095.45, '6000-7000': 13629.27, '7000-8000': 19490.37, '8000-9000': 35577.82, '9000-10000': 27243.68, '10000-11000': 18524.63, '11000-12000': 15339.13, '12000-13000': 22117.97, '13000-14000': 21869.11, '14000-15000': 9146.49, '15000-16000': 6271.75, '16000-17000': 7843.4, '17000-18000': 3631.99, '18000-19000': 1982.3, '19000-20000': 3745.23, '20000-21000': 2715.54, '21000-22000': 324.97, '22000-23000': 751.65, '23000-24000': 552.19, '24000-25000': 614.73, '32000-33000': 93.65, '&gt;40000': 932.81}</t>
   </si>
   <si>
@@ -1516,6 +1729,93 @@
     <t>{'&lt;2000': 16818.32}</t>
   </si>
   <si>
+    <t>{'&lt;2000': 379, '2000-3000': 44, '3000-4000': 47}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 13, '2000-3000': 5, '3000-4000': 171, '4000-5000': 125, '5000-6000': 152, '6000-7000': 275, '7000-8000': 722, '8000-9000': 735, '9000-10000': 474, '10000-11000': 180, '11000-12000': 95, '12000-13000': 20, '13000-14000': 11, '14000-15000': 7, '15000-16000': 6, '16000-17000': 2, '17000-18000': 3, '18000-19000': 1, '20000-21000': 1, '21000-22000': 1, '25000-26000': 1, '39000-40000': 1}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 150, '2000-3000': 5, '3000-4000': 18, '4000-5000': 38, '5000-6000': 26, '6000-7000': 40, '7000-8000': 31, '8000-9000': 24, '9000-10000': 51, '10000-11000': 49, '11000-12000': 114, '12000-13000': 73, '13000-14000': 91, '14000-15000': 92, '15000-16000': 105, '16000-17000': 53, '17000-18000': 50, '18000-19000': 38, '19000-20000': 39, '20000-21000': 10, '21000-22000': 23, '22000-23000': 15, '23000-24000': 7, '24000-25000': 3, '25000-26000': 4, '26000-27000': 2, '28000-29000': 2, '29000-30000': 1, '30000-31000': 1}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 397167097.0, '2000-3000': 96656513.0, '3000-4000': 114167680.0}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 3947000.0, '2000-3000': 5067000.0, '3000-4000': 277517283.0, '4000-5000': 238774800.0, '5000-6000': 347870403.0, '6000-7000': 788395059.0, '7000-8000': 2369041862.0, '8000-9000': 2585832128.0, '9000-10000': 1814294198.0, '10000-11000': 739977788.0, '11000-12000': 446322555.0, '12000-13000': 89508986.0, '13000-14000': 48035700.0, '14000-15000': 37578200.0, '15000-16000': 31690000.0, '16000-17000': 12885000.0, '17000-18000': 18550000.0, '18000-19000': 7500000.0, '20000-21000': 6850000.0, '21000-22000': 7160000.0, '25000-26000': 8500000.0, '39000-40000': 8100000.0}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 3931080.0, '2000-3000': 4450000.0, '3000-4000': 23646000.0, '4000-5000': 61927500.0, '5000-6000': 51560611.0, '6000-7000': 98910600.0, '7000-8000': 89557000.0, '8000-9000': 78535000.0, '9000-10000': 187548451.0, '10000-11000': 203450000.0, '11000-12000': 512754000.0, '12000-13000': 343521000.0, '13000-14000': 471210000.0, '14000-15000': 508191600.0, '15000-16000': 607585000.0, '16000-17000': 330842000.0, '17000-18000': 328040000.0, '18000-19000': 260960000.0, '19000-20000': 278015000.0, '20000-21000': 72350000.0, '21000-22000': 178075000.0, '22000-23000': 116425000.0, '23000-24000': 56940000.0, '24000-25000': 22500000.0, '25000-26000': 34750000.0, '26000-27000': 17000000.0, '28000-29000': 20000000.0, '29000-30000': 12300000.0, '30000-31000': 10700000.0}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 301908.67, '2000-3000': 34495.71, '3000-4000': 36381.46}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 5204.5, '2000-3000': 1956.68, '3000-4000': 77155.49, '4000-5000': 52418.2, '5000-6000': 63575.31, '6000-7000': 120529.03, '7000-8000': 314626.02, '8000-9000': 303552.87, '9000-10000': 192267.54, '10000-11000': 71432.49, '11000-12000': 39014.76, '12000-13000': 7125.23, '13000-14000': 3598.51, '14000-15000': 2625.23, '15000-16000': 2067.44, '16000-17000': 775.98, '17000-18000': 1055.95, '18000-19000': 400.64, '20000-21000': 334.76, '21000-22000': 340.03, '25000-26000': 331.75, '39000-40000': 206.24}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 57701.97, '2000-3000': 1784.89, '3000-4000': 6591.23, '4000-5000': 13469.37, '5000-6000': 9176.85, '6000-7000': 15313.94, '7000-8000': 11910.37, '8000-9000': 9194.5, '9000-10000': 19733.96, '10000-11000': 19473.37, '11000-12000': 44752.08, '12000-13000': 27526.13, '13000-14000': 34816.16, '14000-15000': 34929.72, '15000-16000': 39244.79, '16000-17000': 20091.97, '17000-18000': 18715.58, '18000-19000': 14191.8, '19000-20000': 14258.86, '20000-21000': 3542.43, '21000-22000': 8296.03, '22000-23000': 5190.94, '23000-24000': 2444.28, '24000-25000': 907.19, '25000-26000': 1368.0, '26000-27000': 634.43, '28000-29000': 696.86, '29000-30000': 422.92, '30000-31000': 350.05}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 126, '2000-3000': 80, '3000-4000': 23}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 50, '2000-3000': 12, '3000-4000': 77, '4000-5000': 359, '5000-6000': 448, '6000-7000': 956, '7000-8000': 3139, '8000-9000': 2866, '9000-10000': 1499, '10000-11000': 795, '11000-12000': 330, '12000-13000': 57, '13000-14000': 16, '14000-15000': 4, '15000-16000': 4, '16000-17000': 7, '17000-18000': 1, '19000-20000': 2, '30000-31000': 1}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 122, '2000-3000': 7, '3000-4000': 18, '4000-5000': 25, '5000-6000': 33, '6000-7000': 20, '7000-8000': 39, '8000-9000': 95, '9000-10000': 99, '10000-11000': 125, '11000-12000': 122, '12000-13000': 121, '13000-14000': 100, '14000-15000': 81, '15000-16000': 32, '16000-17000': 41, '17000-18000': 20, '18000-19000': 22, '19000-20000': 35, '20000-21000': 17, '21000-22000': 13, '22000-23000': 10, '23000-24000': 10, '24000-25000': 3, '25000-26000': 4, '26000-27000': 6, '27000-28000': 3, '28000-29000': 1, '29000-30000': 1, '31000-32000': 1, '33000-34000': 2, '35000-36000': 2, '36000-37000': 1}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 253671080.0, '2000-3000': 292068046.0, '3000-4000': 93562960.0}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 29488091.0, '2000-3000': 18182355.0, '3000-4000': 167931246.0, '4000-5000': 981315100.0, '5000-6000': 1542612328.0, '6000-7000': 4068476546.0, '7000-8000': 14643642637.0, '8000-9000': 14546092939.0, '9000-10000': 8449031064.0, '10000-11000': 5304992429.0, '11000-12000': 2270602965.0, '12000-13000': 418931303.0, '13000-14000': 138910824.0, '14000-15000': 35150100.0, '15000-16000': 42605995.0, '16000-17000': 76370842.0, '17000-18000': 10200000.0, '19000-20000': 23108880.0, '30000-31000': 18792600.0}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 5210941.0, '2000-3000': 9350000.0, '3000-4000': 34881000.0, '4000-5000': 59345000.0, '5000-6000': 98207000.0, '6000-7000': 72675000.0, '7000-8000': 158089400.0, '8000-9000': 460491361.0, '9000-10000': 512685000.0, '10000-11000': 713231000.0, '11000-12000': 791596500.0, '12000-13000': 812579275.0, '13000-14000': 754266800.0, '14000-15000': 659600000.0, '15000-16000': 310691000.0, '16000-17000': 373400000.0, '17000-18000': 212551000.0, '18000-19000': 231630000.0, '19000-20000': 367560000.0, '20000-21000': 188499999.0, '21000-22000': 162690000.0, '22000-23000': 125051000.0, '23000-24000': 132900000.0, '24000-25000': 39800000.0, '25000-26000': 58150000.0, '26000-27000': 78285000.0, '27000-28000': 48850000.0, '28000-29000': 14400000.0, '29000-30000': 16250000.0, '31000-32000': 20800000.0, '33000-34000': 43600000.0, '35000-36000': 46000000.0, '36000-37000': 23000000.0}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 170481.85, '2000-3000': 113114.14, '3000-4000': 30067.4}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 30727.24, '2000-3000': 7344.28, '3000-4000': 46550.96, '4000-5000': 211530.25, '5000-6000': 278301.39, '6000-7000': 613011.74, '7000-8000': 1943704.46, '8000-9000': 1716051.45, '9000-10000': 897276.92, '10000-11000': 506208.32, '11000-12000': 198882.88, '12000-13000': 33822.21, '13000-14000': 10165.2, '14000-15000': 2431.16, '15000-16000': 2756.34, '16000-17000': 4605.81, '17000-18000': 583.52, '19000-20000': 1202.23, '30000-31000': 610.32}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 67434.67, '2000-3000': 3742.75, '3000-4000': 9572.86, '4000-5000': 13316.14, '5000-6000': 18180.18, '6000-7000': 11092.62, '7000-8000': 21085.49, '8000-9000': 53599.34, '9000-10000': 54005.71, '10000-11000': 68069.22, '11000-12000': 68773.99, '12000-13000': 64990.56, '13000-14000': 55971.94, '14000-15000': 45443.67, '15000-16000': 20008.66, '16000-17000': 22672.0, '17000-18000': 12164.5, '18000-19000': 12539.74, '19000-20000': 18981.24, '20000-21000': 9134.22, '21000-22000': 7537.6, '22000-23000': 5540.12, '23000-24000': 5675.75, '24000-25000': 1629.02, '25000-26000': 2279.71, '26000-27000': 2938.25, '27000-28000': 1778.54, '28000-29000': 503.97, '29000-30000': 552.84, '31000-32000': 658.97, '33000-34000': 1304.6, '35000-36000': 1277.9, '36000-37000': 622.37}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 1, '2000-3000': 25, '3000-4000': 2}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 44, '2000-3000': 16, '3000-4000': 32, '4000-5000': 142, '5000-6000': 243, '6000-7000': 253, '7000-8000': 770, '8000-9000': 965, '9000-10000': 652, '10000-11000': 375, '11000-12000': 187, '12000-13000': 137, '13000-14000': 20, '14000-15000': 4, '15000-16000': 9, '16000-17000': 1, '17000-18000': 4, '18000-19000': 2, '19000-20000': 1}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 63, '3000-4000': 2, '4000-5000': 1, '5000-6000': 7, '6000-7000': 9, '7000-8000': 32, '8000-9000': 18, '9000-10000': 54, '10000-11000': 61, '11000-12000': 69, '12000-13000': 60, '13000-14000': 66, '14000-15000': 62, '15000-16000': 34, '16000-17000': 16, '17000-18000': 16, '18000-19000': 7, '19000-20000': 16, '20000-21000': 9, '21000-22000': 10, '22000-23000': 13, '23000-24000': 7, '24000-25000': 10, '25000-26000': 10, '26000-27000': 11, '27000-28000': 10, '28000-29000': 1, '29000-30000': 3, '30000-31000': 2, '31000-32000': 2, '33000-34000': 1}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 3356432.0, '2000-3000': 129971287.0, '3000-4000': 11143000.0}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 43834240.0, '2000-3000': 40627550.0, '3000-4000': 104771800.0, '4000-5000': 595525875.0, '5000-6000': 1224985754.0, '6000-7000': 1496407194.0, '7000-8000': 5142581147.0, '8000-9000': 7064037479.0, '9000-10000': 5309478940.0, '10000-11000': 3525605050.0, '11000-12000': 2052728169.0, '12000-13000': 1452779268.0, '13000-14000': 256952213.0, '14000-15000': 48295125.0, '15000-16000': 122041231.0, '16000-17000': 17000000.0, '17000-18000': 63300000.0, '18000-19000': 29000000.0, '19000-20000': 18621601.0}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 4978234.0, '3000-4000': 5000000.0, '4000-5000': 3700000.0, '5000-6000': 34364500.0, '6000-7000': 47220000.0, '7000-8000': 210174000.0, '8000-9000': 127791000.0, '9000-10000': 436191000.0, '10000-11000': 541004000.0, '11000-12000': 652055000.0, '12000-13000': 630901000.0, '13000-14000': 780563751.0, '14000-15000': 780481000.0, '15000-16000': 440039000.0, '16000-17000': 242417925.0, '17000-18000': 230597960.0, '18000-19000': 113650000.0, '19000-20000': 278432038.0, '20000-21000': 158800714.0, '21000-22000': 175005885.0, '22000-23000': 243511221.0, '23000-24000': 114288445.0, '24000-25000': 196696328.0, '25000-26000': 190736267.0, '26000-27000': 219160906.0, '27000-28000': 210305751.0, '28000-29000': 20300000.0, '29000-30000': 68877682.0, '30000-31000': 52824092.0, '31000-32000': 50000000.0, '33000-34000': 28640000.0}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 2591.22, '2000-3000': 49204.5, '3000-4000': 3709.7}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 41364.22, '2000-3000': 15257.75, '3000-4000': 29258.7, '4000-5000': 130861.72, '5000-6000': 222940.37, '6000-7000': 230203.96, '7000-8000': 677697.89, '8000-9000': 835166.17, '9000-10000': 561188.78, '10000-11000': 337624.05, '11000-12000': 178969.69, '12000-13000': 116782.19, '13000-14000': 19305.56, '14000-15000': 3351.26, '15000-16000': 7886.46, '16000-17000': 1004.71, '17000-18000': 3629.19, '18000-19000': 1591.35, '19000-20000': 969.19}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 51625.92, '3000-4000': 1428.6, '4000-5000': 743.25, '5000-6000': 6070.36, '6000-7000': 7067.21, '7000-8000': 27712.46, '8000-9000': 14952.92, '9000-10000': 45634.41, '10000-11000': 51813.79, '11000-12000': 57168.25, '12000-13000': 50680.68, '13000-14000': 57631.42, '14000-15000': 53612.25, '15000-16000': 28393.82, '16000-17000': 14730.86, '17000-18000': 13292.36, '18000-19000': 6091.24, '19000-20000': 14179.31, '20000-21000': 7722.74, '21000-22000': 8087.75, '22000-23000': 10864.97, '23000-24000': 4845.52, '24000-25000': 7999.59, '25000-26000': 7532.22, '26000-27000': 8192.7, '27000-28000': 7668.81, '28000-29000': 718.93, '29000-30000': 2326.96, '30000-31000': 1744.41, '31000-32000': 1581.02, '33000-34000': 860.15}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 8956369.0}</t>
+  </si>
+  <si>
+    <t>{'&lt;2000': 7224.47}</t>
+  </si>
+  <si>
     <t>{'6000-7000': 1, '8000-9000': 4, '9000-10000': 1}</t>
   </si>
   <si>
@@ -1534,24 +1834,6 @@
     <t>{'26000-27000': 402.25}</t>
   </si>
   <si>
-    <t>{'&lt;2000': 13, '2000-3000': 5, '3000-4000': 171, '4000-5000': 125, '5000-6000': 152, '6000-7000': 275, '7000-8000': 722, '8000-9000': 735, '9000-10000': 474, '10000-11000': 180, '11000-12000': 95, '12000-13000': 20, '13000-14000': 11, '14000-15000': 7, '15000-16000': 6, '16000-17000': 2, '17000-18000': 3, '18000-19000': 1, '20000-21000': 1, '21000-22000': 1, '25000-26000': 1, '39000-40000': 1}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 150, '2000-3000': 5, '3000-4000': 18, '4000-5000': 38, '5000-6000': 26, '6000-7000': 40, '7000-8000': 31, '8000-9000': 24, '9000-10000': 51, '10000-11000': 49, '11000-12000': 114, '12000-13000': 73, '13000-14000': 91, '14000-15000': 92, '15000-16000': 105, '16000-17000': 53, '17000-18000': 50, '18000-19000': 38, '19000-20000': 39, '20000-21000': 10, '21000-22000': 23, '22000-23000': 15, '23000-24000': 7, '24000-25000': 3, '25000-26000': 4, '26000-27000': 2, '28000-29000': 2, '29000-30000': 1, '30000-31000': 1}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 3947000.0, '2000-3000': 5067000.0, '3000-4000': 277517283.0, '4000-5000': 238774800.0, '5000-6000': 347870403.0, '6000-7000': 788395059.0, '7000-8000': 2369041862.0, '8000-9000': 2585832128.0, '9000-10000': 1814294198.0, '10000-11000': 739977788.0, '11000-12000': 446322555.0, '12000-13000': 89508986.0, '13000-14000': 48035700.0, '14000-15000': 37578200.0, '15000-16000': 31690000.0, '16000-17000': 12885000.0, '17000-18000': 18550000.0, '18000-19000': 7500000.0, '20000-21000': 6850000.0, '21000-22000': 7160000.0, '25000-26000': 8500000.0, '39000-40000': 8100000.0}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 3931080.0, '2000-3000': 4450000.0, '3000-4000': 23646000.0, '4000-5000': 61927500.0, '5000-6000': 51560611.0, '6000-7000': 98910600.0, '7000-8000': 89557000.0, '8000-9000': 78535000.0, '9000-10000': 187548451.0, '10000-11000': 203450000.0, '11000-12000': 512754000.0, '12000-13000': 343521000.0, '13000-14000': 471210000.0, '14000-15000': 508191600.0, '15000-16000': 607585000.0, '16000-17000': 330842000.0, '17000-18000': 328040000.0, '18000-19000': 260960000.0, '19000-20000': 278015000.0, '20000-21000': 72350000.0, '21000-22000': 178075000.0, '22000-23000': 116425000.0, '23000-24000': 56940000.0, '24000-25000': 22500000.0, '25000-26000': 34750000.0, '26000-27000': 17000000.0, '28000-29000': 20000000.0, '29000-30000': 12300000.0, '30000-31000': 10700000.0}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 5204.5, '2000-3000': 1956.68, '3000-4000': 77155.49, '4000-5000': 52418.2, '5000-6000': 63575.31, '6000-7000': 120529.03, '7000-8000': 314626.02, '8000-9000': 303552.87, '9000-10000': 192267.54, '10000-11000': 71432.49, '11000-12000': 39014.76, '12000-13000': 7125.23, '13000-14000': 3598.51, '14000-15000': 2625.23, '15000-16000': 2067.44, '16000-17000': 775.98, '17000-18000': 1055.95, '18000-19000': 400.64, '20000-21000': 334.76, '21000-22000': 340.03, '25000-26000': 331.75, '39000-40000': 206.24}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 57701.97, '2000-3000': 1784.89, '3000-4000': 6591.23, '4000-5000': 13469.37, '5000-6000': 9176.85, '6000-7000': 15313.94, '7000-8000': 11910.37, '8000-9000': 9194.5, '9000-10000': 19733.96, '10000-11000': 19473.37, '11000-12000': 44752.08, '12000-13000': 27526.13, '13000-14000': 34816.16, '14000-15000': 34929.72, '15000-16000': 39244.79, '16000-17000': 20091.97, '17000-18000': 18715.58, '18000-19000': 14191.8, '19000-20000': 14258.86, '20000-21000': 3542.43, '21000-22000': 8296.03, '22000-23000': 5190.94, '23000-24000': 2444.28, '24000-25000': 907.19, '25000-26000': 1368.0, '26000-27000': 634.43, '28000-29000': 696.86, '29000-30000': 422.92, '30000-31000': 350.05}</t>
-  </si>
-  <si>
     <t>{'7000-8000': 15, '8000-9000': 16, '9000-10000': 21, '10000-11000': 2}</t>
   </si>
   <si>
@@ -1559,42 +1841,6 @@
   </si>
   <si>
     <t>{'7000-8000': 11380.88, '8000-9000': 12449.86, '9000-10000': 16980.43, '10000-11000': 1617.18}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 50, '2000-3000': 12, '3000-4000': 77, '4000-5000': 359, '5000-6000': 448, '6000-7000': 956, '7000-8000': 3139, '8000-9000': 2866, '9000-10000': 1499, '10000-11000': 795, '11000-12000': 330, '12000-13000': 57, '13000-14000': 16, '14000-15000': 4, '15000-16000': 4, '16000-17000': 7, '17000-18000': 1, '19000-20000': 2, '30000-31000': 1}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 122, '2000-3000': 7, '3000-4000': 18, '4000-5000': 25, '5000-6000': 33, '6000-7000': 20, '7000-8000': 39, '8000-9000': 95, '9000-10000': 99, '10000-11000': 125, '11000-12000': 122, '12000-13000': 121, '13000-14000': 100, '14000-15000': 81, '15000-16000': 32, '16000-17000': 41, '17000-18000': 20, '18000-19000': 22, '19000-20000': 35, '20000-21000': 17, '21000-22000': 13, '22000-23000': 10, '23000-24000': 10, '24000-25000': 3, '25000-26000': 4, '26000-27000': 6, '27000-28000': 3, '28000-29000': 1, '29000-30000': 1, '31000-32000': 1, '33000-34000': 2, '35000-36000': 2, '36000-37000': 1}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 29488091.0, '2000-3000': 18182355.0, '3000-4000': 167931246.0, '4000-5000': 981315100.0, '5000-6000': 1542612328.0, '6000-7000': 4068476546.0, '7000-8000': 14643642637.0, '8000-9000': 14546092939.0, '9000-10000': 8449031064.0, '10000-11000': 5304992429.0, '11000-12000': 2270602965.0, '12000-13000': 418931303.0, '13000-14000': 138910824.0, '14000-15000': 35150100.0, '15000-16000': 42605995.0, '16000-17000': 76370842.0, '17000-18000': 10200000.0, '19000-20000': 23108880.0, '30000-31000': 18792600.0}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 5210941.0, '2000-3000': 9350000.0, '3000-4000': 34881000.0, '4000-5000': 59345000.0, '5000-6000': 98207000.0, '6000-7000': 72675000.0, '7000-8000': 158089400.0, '8000-9000': 460491361.0, '9000-10000': 512685000.0, '10000-11000': 713231000.0, '11000-12000': 791596500.0, '12000-13000': 812579275.0, '13000-14000': 754266800.0, '14000-15000': 659600000.0, '15000-16000': 310691000.0, '16000-17000': 373400000.0, '17000-18000': 212551000.0, '18000-19000': 231630000.0, '19000-20000': 367560000.0, '20000-21000': 188499999.0, '21000-22000': 162690000.0, '22000-23000': 125051000.0, '23000-24000': 132900000.0, '24000-25000': 39800000.0, '25000-26000': 58150000.0, '26000-27000': 78285000.0, '27000-28000': 48850000.0, '28000-29000': 14400000.0, '29000-30000': 16250000.0, '31000-32000': 20800000.0, '33000-34000': 43600000.0, '35000-36000': 46000000.0, '36000-37000': 23000000.0}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 30727.24, '2000-3000': 7344.28, '3000-4000': 46550.96, '4000-5000': 211530.25, '5000-6000': 278301.39, '6000-7000': 613011.74, '7000-8000': 1943704.46, '8000-9000': 1716051.45, '9000-10000': 897276.92, '10000-11000': 506208.32, '11000-12000': 198882.88, '12000-13000': 33822.21, '13000-14000': 10165.2, '14000-15000': 2431.16, '15000-16000': 2756.34, '16000-17000': 4605.81, '17000-18000': 583.52, '19000-20000': 1202.23, '30000-31000': 610.32}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 67434.67, '2000-3000': 3742.75, '3000-4000': 9572.86, '4000-5000': 13316.14, '5000-6000': 18180.18, '6000-7000': 11092.62, '7000-8000': 21085.49, '8000-9000': 53599.34, '9000-10000': 54005.71, '10000-11000': 68069.22, '11000-12000': 68773.99, '12000-13000': 64990.56, '13000-14000': 55971.94, '14000-15000': 45443.67, '15000-16000': 20008.66, '16000-17000': 22672.0, '17000-18000': 12164.5, '18000-19000': 12539.74, '19000-20000': 18981.24, '20000-21000': 9134.22, '21000-22000': 7537.6, '22000-23000': 5540.12, '23000-24000': 5675.75, '24000-25000': 1629.02, '25000-26000': 2279.71, '26000-27000': 2938.25, '27000-28000': 1778.54, '28000-29000': 503.97, '29000-30000': 552.84, '31000-32000': 658.97, '33000-34000': 1304.6, '35000-36000': 1277.9, '36000-37000': 622.37}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 44, '2000-3000': 16, '3000-4000': 32, '4000-5000': 142, '5000-6000': 243, '6000-7000': 253, '7000-8000': 770, '8000-9000': 965, '9000-10000': 652, '10000-11000': 375, '11000-12000': 187, '12000-13000': 137, '13000-14000': 20, '14000-15000': 4, '15000-16000': 9, '16000-17000': 1, '17000-18000': 4, '18000-19000': 2, '19000-20000': 1}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 63, '3000-4000': 2, '4000-5000': 1, '5000-6000': 7, '6000-7000': 9, '7000-8000': 32, '8000-9000': 18, '9000-10000': 54, '10000-11000': 61, '11000-12000': 69, '12000-13000': 60, '13000-14000': 66, '14000-15000': 62, '15000-16000': 34, '16000-17000': 16, '17000-18000': 16, '18000-19000': 7, '19000-20000': 16, '20000-21000': 9, '21000-22000': 10, '22000-23000': 13, '23000-24000': 7, '24000-25000': 10, '25000-26000': 10, '26000-27000': 11, '27000-28000': 10, '28000-29000': 1, '29000-30000': 3, '30000-31000': 2, '31000-32000': 2, '33000-34000': 1}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 43834240.0, '2000-3000': 40627550.0, '3000-4000': 104771800.0, '4000-5000': 595525875.0, '5000-6000': 1224985754.0, '6000-7000': 1496407194.0, '7000-8000': 5142581147.0, '8000-9000': 7064037479.0, '9000-10000': 5309478940.0, '10000-11000': 3525605050.0, '11000-12000': 2052728169.0, '12000-13000': 1452779268.0, '13000-14000': 256952213.0, '14000-15000': 48295125.0, '15000-16000': 122041231.0, '16000-17000': 17000000.0, '17000-18000': 63300000.0, '18000-19000': 29000000.0, '19000-20000': 18621601.0}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 4978234.0, '3000-4000': 5000000.0, '4000-5000': 3700000.0, '5000-6000': 34364500.0, '6000-7000': 47220000.0, '7000-8000': 210174000.0, '8000-9000': 127791000.0, '9000-10000': 436191000.0, '10000-11000': 541004000.0, '11000-12000': 652055000.0, '12000-13000': 630901000.0, '13000-14000': 780563751.0, '14000-15000': 780481000.0, '15000-16000': 440039000.0, '16000-17000': 242417925.0, '17000-18000': 230597960.0, '18000-19000': 113650000.0, '19000-20000': 278432038.0, '20000-21000': 158800714.0, '21000-22000': 175005885.0, '22000-23000': 243511221.0, '23000-24000': 114288445.0, '24000-25000': 196696328.0, '25000-26000': 190736267.0, '26000-27000': 219160906.0, '27000-28000': 210305751.0, '28000-29000': 20300000.0, '29000-30000': 68877682.0, '30000-31000': 52824092.0, '31000-32000': 50000000.0, '33000-34000': 28640000.0}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 41364.22, '2000-3000': 15257.75, '3000-4000': 29258.7, '4000-5000': 130861.72, '5000-6000': 222940.37, '6000-7000': 230203.96, '7000-8000': 677697.89, '8000-9000': 835166.17, '9000-10000': 561188.78, '10000-11000': 337624.05, '11000-12000': 178969.69, '12000-13000': 116782.19, '13000-14000': 19305.56, '14000-15000': 3351.26, '15000-16000': 7886.46, '16000-17000': 1004.71, '17000-18000': 3629.19, '18000-19000': 1591.35, '19000-20000': 969.19}</t>
-  </si>
-  <si>
-    <t>{'&lt;2000': 51625.92, '3000-4000': 1428.6, '4000-5000': 743.25, '5000-6000': 6070.36, '6000-7000': 7067.21, '7000-8000': 27712.46, '8000-9000': 14952.92, '9000-10000': 45634.41, '10000-11000': 51813.79, '11000-12000': 57168.25, '12000-13000': 50680.68, '13000-14000': 57631.42, '14000-15000': 53612.25, '15000-16000': 28393.82, '16000-17000': 14730.86, '17000-18000': 13292.36, '18000-19000': 6091.24, '19000-20000': 14179.31, '20000-21000': 7722.74, '21000-22000': 8087.75, '22000-23000': 10864.97, '23000-24000': 4845.52, '24000-25000': 7999.59, '25000-26000': 7532.22, '26000-27000': 8192.7, '27000-28000': 7668.81, '28000-29000': 718.93, '29000-30000': 2326.96, '30000-31000': 1744.41, '31000-32000': 1581.02, '33000-34000': 860.15}</t>
   </si>
   <si>
     <t>{'5000-6000': 1, '6000-7000': 5, '7000-8000': 33, '8000-9000': 30, '9000-10000': 39, '10000-11000': 5, '11000-12000': 13, '12000-13000': 1}</t>
@@ -2151,10 +2397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:JL4"/>
+  <dimension ref="A1:KG5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:272">
+    <row r="1" spans="1:293">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2971,1224 +3217,900 @@
       <c r="JL1" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="JM1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="JN1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="JO1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="JP1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="JQ1" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="JR1" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="JS1" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="JT1" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="JU1" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="JV1" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="JW1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="JX1" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="JY1" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="JZ1" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="KA1" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="KB1" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="KC1" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="KD1" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="KE1" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="KF1" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="KG1" s="1" t="s">
+        <v>292</v>
+      </c>
     </row>
-    <row r="2" spans="1:272">
+    <row r="2" spans="1:293">
       <c r="A2" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="B2">
-        <v>127069240137</v>
+        <v>1487287579</v>
       </c>
       <c r="C2">
-        <v>19868329.78</v>
+        <v>802387.74</v>
       </c>
       <c r="D2">
-        <v>22220</v>
-      </c>
-      <c r="E2">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>45657</v>
+        <v>46062</v>
       </c>
       <c r="G2" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="H2">
-        <v>18511</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>546</v>
-      </c>
-      <c r="J2">
-        <v>1679</v>
-      </c>
-      <c r="K2">
-        <v>1484</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>96387069885</v>
+        <v>1405835991</v>
       </c>
       <c r="M2">
-        <v>2550492510</v>
-      </c>
-      <c r="N2">
-        <v>23005753968</v>
-      </c>
-      <c r="O2">
-        <v>5125923774</v>
+        <v>81451588</v>
       </c>
       <c r="P2">
-        <v>5334093.52</v>
+        <v>1894657.67</v>
       </c>
       <c r="Q2">
-        <v>4697039.61</v>
-      </c>
-      <c r="R2">
-        <v>14690775.2</v>
-      </c>
-      <c r="S2">
-        <v>3527820.9</v>
+        <v>5817970.57</v>
       </c>
       <c r="T2">
-        <v>13245903.43</v>
+        <v>755164.14</v>
       </c>
       <c r="U2">
-        <v>249580.35</v>
-      </c>
-      <c r="V2">
-        <v>5508493.68</v>
-      </c>
-      <c r="W2">
-        <v>864352.3199999999</v>
-      </c>
-      <c r="X2">
-        <v>6</v>
+        <v>47223.61</v>
       </c>
       <c r="Y2">
-        <v>3049</v>
-      </c>
-      <c r="Z2">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>10919</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>3870</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>127</v>
-      </c>
-      <c r="AD2">
-        <v>29778521</v>
-      </c>
-      <c r="AE2">
-        <v>9893397962</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>371565218</v>
-      </c>
-      <c r="AG2">
-        <v>52786438244</v>
+        <v>607991290</v>
       </c>
       <c r="AH2">
-        <v>28608572636</v>
+        <v>639302086</v>
       </c>
       <c r="AI2">
-        <v>1405493217</v>
+        <v>144470719</v>
       </c>
       <c r="AJ2">
-        <v>4963086.83</v>
-      </c>
-      <c r="AK2">
-        <v>3296700.42</v>
-      </c>
-      <c r="AL2">
-        <v>6880837.37</v>
+        <v>8956369</v>
       </c>
       <c r="AM2">
-        <v>4969070.72</v>
-      </c>
-      <c r="AN2">
-        <v>7417312.07</v>
+        <v>1293598.49</v>
       </c>
       <c r="AO2">
-        <v>11066875.72</v>
+        <v>2791712.17</v>
       </c>
       <c r="AP2">
-        <v>3514.66</v>
+        <v>5159668.54</v>
       </c>
       <c r="AQ2">
-        <v>1280354.33</v>
-      </c>
-      <c r="AR2">
-        <v>42428.35</v>
-      </c>
-      <c r="AS2">
-        <v>6682406.27</v>
+        <v>4478184.5</v>
       </c>
       <c r="AT2">
-        <v>3427583.28</v>
-      </c>
-      <c r="AU2">
-        <v>156276.27</v>
+        <v>372785.84</v>
       </c>
       <c r="AV2">
-        <v>470</v>
+        <v>313663.39</v>
       </c>
       <c r="AW2">
-        <v>59</v>
+        <v>55505.43</v>
       </c>
       <c r="AX2">
-        <v>1</v>
-      </c>
-      <c r="AY2">
-        <v>31</v>
-      </c>
-      <c r="AZ2">
-        <v>3</v>
-      </c>
-      <c r="BA2">
-        <v>17960</v>
-      </c>
-      <c r="BB2">
-        <v>81</v>
-      </c>
-      <c r="BC2">
-        <v>44</v>
-      </c>
-      <c r="BD2">
-        <v>546</v>
-      </c>
-      <c r="BF2">
-        <v>53</v>
-      </c>
-      <c r="BG2">
-        <v>42</v>
+        <v>7224.47</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
       </c>
       <c r="BH2">
-        <v>104</v>
-      </c>
-      <c r="BI2">
-        <v>1483</v>
-      </c>
-      <c r="BJ2">
-        <v>1</v>
-      </c>
-      <c r="BL2">
-        <v>27</v>
-      </c>
-      <c r="BM2">
-        <v>1752</v>
-      </c>
-      <c r="BN2">
-        <v>7044</v>
-      </c>
-      <c r="BO2">
-        <v>22220</v>
-      </c>
-      <c r="BP2">
-        <v>42653.27</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>11341.01</v>
-      </c>
-      <c r="BR2">
-        <v>4867392.22</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>10406.24</v>
-      </c>
-      <c r="BT2">
-        <v>8157.93</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>11048.28</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>5656.13</v>
+        <v>1769.62</v>
       </c>
       <c r="BW2">
-        <v>8484.23</v>
-      </c>
-      <c r="BX2">
-        <v>9180.07</v>
-      </c>
-      <c r="BY2">
-        <v>13450.63</v>
+        <v>1724.81</v>
       </c>
       <c r="BZ2">
-        <v>16928.92</v>
+        <v>1549.58</v>
       </c>
       <c r="CA2">
-        <v>14618.77</v>
-      </c>
-      <c r="CB2">
-        <v>10383.06</v>
-      </c>
-      <c r="CC2">
-        <v>16459.06</v>
+        <v>1789.89</v>
       </c>
       <c r="CD2">
-        <v>18382163.94</v>
+        <v>2436.15</v>
       </c>
       <c r="CE2">
-        <v>20113.07</v>
-      </c>
-      <c r="CF2">
-        <v>340088.7166021238</v>
-      </c>
-      <c r="CG2">
-        <v>87196.1697824516</v>
+        <v>2104.88</v>
       </c>
       <c r="CH2">
-        <v>38809340.62770963</v>
+        <v>2992.14</v>
       </c>
       <c r="CI2">
-        <v>80009.14266053283</v>
-      </c>
-      <c r="CJ2">
-        <v>65045.89</v>
-      </c>
-      <c r="CK2">
-        <v>84945.50999999999</v>
+        <v>2371.7</v>
       </c>
       <c r="CL2">
-        <v>45098.23</v>
+        <v>14109.79516044934</v>
       </c>
       <c r="CM2">
-        <v>65231.57</v>
-      </c>
-      <c r="CN2">
-        <v>73195.73</v>
-      </c>
-      <c r="CO2">
-        <v>103416.1</v>
+        <v>13261.29899258424</v>
       </c>
       <c r="CP2">
-        <v>134979.93</v>
+        <v>12355.29</v>
       </c>
       <c r="CQ2">
-        <v>112397.44</v>
-      </c>
-      <c r="CR2">
-        <v>82787.59</v>
-      </c>
-      <c r="CS2">
-        <v>126546.68</v>
+        <v>13761.69</v>
       </c>
       <c r="CT2">
-        <v>146567120.48</v>
+        <v>19424.23</v>
       </c>
       <c r="CU2">
-        <v>154640.8</v>
-      </c>
-      <c r="CV2" t="s">
-        <v>276</v>
-      </c>
-      <c r="CW2" t="s">
-        <v>279</v>
-      </c>
-      <c r="CX2" t="s">
-        <v>281</v>
-      </c>
-      <c r="CY2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>285</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>288</v>
+        <v>16183.52</v>
+      </c>
+      <c r="CX2">
+        <v>23857.32</v>
+      </c>
+      <c r="CY2">
+        <v>18234.95</v>
       </c>
       <c r="DB2" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="DC2" t="s">
-        <v>294</v>
-      </c>
-      <c r="DD2" t="s">
-        <v>297</v>
-      </c>
-      <c r="DE2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="DF2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="DG2" t="s">
-        <v>306</v>
-      </c>
-      <c r="DH2">
-        <v>8425.74</v>
-      </c>
-      <c r="DI2">
-        <v>7918.66</v>
-      </c>
-      <c r="DJ2">
-        <v>8735.780000000001</v>
-      </c>
-      <c r="DK2">
-        <v>8119.53</v>
-      </c>
-      <c r="DL2">
-        <v>8394.98</v>
-      </c>
-      <c r="DM2">
-        <v>8852.530000000001</v>
-      </c>
-      <c r="DN2">
-        <v>8604.290000000001</v>
+        <v>311</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>321</v>
+      </c>
+      <c r="DK2" t="s">
+        <v>325</v>
       </c>
       <c r="DO2">
-        <v>8052.99</v>
-      </c>
-      <c r="DP2">
-        <v>8627.58</v>
+        <v>1621.25</v>
       </c>
       <c r="DQ2">
-        <v>8098.93</v>
+        <v>2026.66</v>
       </c>
       <c r="DR2">
-        <v>8391.209999999999</v>
+        <v>2614.95</v>
       </c>
       <c r="DS2">
-        <v>8905.469999999999</v>
-      </c>
-      <c r="DT2">
-        <v>8817.67</v>
-      </c>
-      <c r="DU2">
-        <v>9091.65</v>
+        <v>1240.31</v>
       </c>
       <c r="DV2">
-        <v>9575</v>
-      </c>
-      <c r="DW2">
-        <v>9029.139999999999</v>
+        <v>1489.07</v>
       </c>
       <c r="DX2">
-        <v>9613.360000000001</v>
+        <v>1929.93</v>
       </c>
       <c r="DY2">
-        <v>9576.09</v>
+        <v>2659.38</v>
       </c>
       <c r="DZ2">
-        <v>9124.360000000001</v>
-      </c>
-      <c r="EA2">
-        <v>10096.78</v>
-      </c>
-      <c r="EB2">
-        <v>9766.73</v>
+        <v>1240.31</v>
       </c>
       <c r="EC2">
-        <v>10178.73</v>
-      </c>
-      <c r="ED2">
-        <v>10890.07</v>
+        <v>1678.86</v>
       </c>
       <c r="EE2">
-        <v>11176.41</v>
-      </c>
-      <c r="EF2" t="s">
-        <v>309</v>
-      </c>
-      <c r="EG2" t="s">
-        <v>312</v>
-      </c>
-      <c r="EH2" t="s">
-        <v>315</v>
-      </c>
-      <c r="EI2" t="s">
-        <v>318</v>
-      </c>
-      <c r="EJ2" t="s">
-        <v>321</v>
-      </c>
-      <c r="EK2" t="s">
-        <v>324</v>
-      </c>
-      <c r="EL2" t="s">
-        <v>327</v>
-      </c>
-      <c r="EM2" t="s">
-        <v>330</v>
-      </c>
-      <c r="EN2" t="s">
-        <v>333</v>
-      </c>
-      <c r="EO2" t="s">
-        <v>336</v>
+        <v>2794.95</v>
+      </c>
+      <c r="EF2">
+        <v>2761.96</v>
+      </c>
+      <c r="EG2">
+        <v>1249.2</v>
+      </c>
+      <c r="EJ2">
+        <v>2999.29</v>
+      </c>
+      <c r="EL2">
+        <v>2993.75</v>
+      </c>
+      <c r="EM2">
+        <v>2893.77</v>
+      </c>
+      <c r="EN2">
+        <v>1254.53</v>
       </c>
       <c r="EP2" t="s">
+        <v>335</v>
+      </c>
+      <c r="EQ2" t="s">
         <v>339</v>
       </c>
-      <c r="EQ2" t="s">
-        <v>342</v>
-      </c>
-      <c r="ER2" t="s">
-        <v>345</v>
-      </c>
-      <c r="ES2" t="s">
-        <v>348</v>
-      </c>
       <c r="ET2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="EU2" t="s">
         <v>353</v>
       </c>
-      <c r="EV2" t="s">
-        <v>356</v>
-      </c>
-      <c r="EW2" t="s">
-        <v>358</v>
-      </c>
       <c r="EX2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="EY2" t="s">
-        <v>361</v>
-      </c>
-      <c r="EZ2" t="s">
-        <v>363</v>
-      </c>
-      <c r="FA2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="FB2" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="FC2" t="s">
-        <v>369</v>
-      </c>
-      <c r="FD2" t="s">
-        <v>371</v>
-      </c>
-      <c r="FE2" t="s">
-        <v>372</v>
-      </c>
-      <c r="FF2" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="FG2" t="s">
-        <v>376</v>
-      </c>
-      <c r="FH2" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="FI2" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="FJ2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="FK2" t="s">
-        <v>383</v>
-      </c>
-      <c r="FL2" t="s">
-        <v>385</v>
-      </c>
-      <c r="FM2" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="FN2" t="s">
-        <v>389</v>
-      </c>
-      <c r="FO2" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="FP2" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="FQ2" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="FR2" t="s">
-        <v>395</v>
-      </c>
-      <c r="FS2" t="s">
-        <v>397</v>
-      </c>
-      <c r="FT2">
-        <v>585.78</v>
-      </c>
-      <c r="FU2">
-        <v>419.93</v>
-      </c>
-      <c r="FV2">
-        <v>785.71</v>
-      </c>
-      <c r="FW2">
-        <v>612</v>
-      </c>
-      <c r="FX2">
-        <v>885.6799999999999</v>
-      </c>
-      <c r="FY2">
-        <v>1230.52</v>
-      </c>
-      <c r="FZ2" t="s">
-        <v>399</v>
-      </c>
-      <c r="GA2" t="s">
-        <v>402</v>
+        <v>417</v>
+      </c>
+      <c r="FU2" t="s">
+        <v>422</v>
+      </c>
+      <c r="FW2" t="s">
+        <v>426</v>
+      </c>
+      <c r="FX2" t="s">
+        <v>429</v>
+      </c>
+      <c r="FY2" t="s">
+        <v>432</v>
       </c>
       <c r="GB2" t="s">
-        <v>405</v>
-      </c>
-      <c r="GC2" t="s">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="GD2" t="s">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="GE2" t="s">
-        <v>414</v>
+        <v>443</v>
       </c>
       <c r="GF2" t="s">
-        <v>417</v>
-      </c>
-      <c r="GG2" t="s">
-        <v>420</v>
-      </c>
-      <c r="GH2" t="s">
-        <v>423</v>
-      </c>
-      <c r="GI2" t="s">
-        <v>426</v>
-      </c>
-      <c r="GJ2" t="s">
-        <v>429</v>
-      </c>
-      <c r="GK2" t="s">
         <v>432</v>
       </c>
-      <c r="GL2" t="s">
-        <v>435</v>
-      </c>
-      <c r="GM2" t="s">
-        <v>437</v>
-      </c>
-      <c r="GN2" t="s">
-        <v>439</v>
+      <c r="GI2">
+        <v>793.16</v>
+      </c>
+      <c r="GK2">
+        <v>1369.71</v>
+      </c>
+      <c r="GL2">
+        <v>1982.34</v>
+      </c>
+      <c r="GM2">
+        <v>3612.24</v>
       </c>
       <c r="GO2" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="GP2" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="GQ2" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="GR2" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="GS2" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="GT2" t="s">
-        <v>449</v>
-      </c>
-      <c r="GU2" t="s">
-        <v>450</v>
-      </c>
-      <c r="GV2" t="s">
-        <v>452</v>
-      </c>
-      <c r="GW2" t="s">
-        <v>454</v>
-      </c>
-      <c r="GX2" t="s">
-        <v>456</v>
-      </c>
-      <c r="GY2" t="s">
-        <v>458</v>
-      </c>
-      <c r="GZ2" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="HA2" t="s">
-        <v>462</v>
+        <v>490</v>
       </c>
       <c r="HB2" t="s">
-        <v>464</v>
+        <v>493</v>
       </c>
       <c r="HC2" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
       <c r="HD2" t="s">
-        <v>468</v>
+        <v>499</v>
       </c>
       <c r="HE2" t="s">
+        <v>502</v>
+      </c>
+      <c r="HF2" t="s">
+        <v>505</v>
+      </c>
+      <c r="HG2" t="s">
+        <v>508</v>
+      </c>
+      <c r="HH2" t="s">
+        <v>511</v>
+      </c>
+      <c r="HI2" t="s">
+        <v>514</v>
+      </c>
+      <c r="HJ2" t="s">
+        <v>517</v>
+      </c>
+      <c r="HK2" t="s">
+        <v>518</v>
+      </c>
+      <c r="HL2" t="s">
+        <v>519</v>
+      </c>
+      <c r="HV2" t="s">
+        <v>321</v>
+      </c>
+      <c r="HW2" t="s">
+        <v>537</v>
+      </c>
+      <c r="HX2" t="s">
+        <v>541</v>
+      </c>
+      <c r="HY2" t="s">
+        <v>325</v>
+      </c>
+      <c r="HZ2" t="s">
+        <v>547</v>
+      </c>
+      <c r="IA2" t="s">
+        <v>551</v>
+      </c>
+      <c r="IH2" t="s">
+        <v>571</v>
+      </c>
+      <c r="II2" t="s">
+        <v>574</v>
+      </c>
+      <c r="IJ2" t="s">
+        <v>577</v>
+      </c>
+      <c r="IK2" t="s">
+        <v>580</v>
+      </c>
+      <c r="IL2" t="s">
+        <v>583</v>
+      </c>
+      <c r="IM2" t="s">
+        <v>586</v>
+      </c>
+      <c r="IN2" t="s">
+        <v>589</v>
+      </c>
+      <c r="IO2" t="s">
+        <v>592</v>
+      </c>
+      <c r="IP2" t="s">
+        <v>595</v>
+      </c>
+      <c r="IQ2" t="s">
+        <v>328</v>
+      </c>
+      <c r="IR2" t="s">
+        <v>598</v>
+      </c>
+      <c r="IS2" t="s">
+        <v>599</v>
+      </c>
+      <c r="JC2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="3" spans="1:293">
+      <c r="A3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B3">
+        <v>127069240137</v>
+      </c>
+      <c r="C3">
+        <v>19868329.78</v>
+      </c>
+      <c r="D3">
+        <v>22220</v>
+      </c>
+      <c r="E3">
+        <v>88</v>
+      </c>
+      <c r="F3" s="2">
+        <v>45657</v>
+      </c>
+      <c r="G3" t="s">
+        <v>297</v>
+      </c>
+      <c r="H3">
+        <v>18511</v>
+      </c>
+      <c r="I3">
+        <v>546</v>
+      </c>
+      <c r="J3">
+        <v>1679</v>
+      </c>
+      <c r="K3">
+        <v>1484</v>
+      </c>
+      <c r="L3">
+        <v>96387069885</v>
+      </c>
+      <c r="M3">
+        <v>2550492510</v>
+      </c>
+      <c r="N3">
+        <v>23005753968</v>
+      </c>
+      <c r="O3">
+        <v>5125923774</v>
+      </c>
+      <c r="P3">
+        <v>5334093.52</v>
+      </c>
+      <c r="Q3">
+        <v>4697039.61</v>
+      </c>
+      <c r="R3">
+        <v>14690775.2</v>
+      </c>
+      <c r="S3">
+        <v>3527820.9</v>
+      </c>
+      <c r="T3">
+        <v>13245903.43</v>
+      </c>
+      <c r="U3">
+        <v>249580.35</v>
+      </c>
+      <c r="V3">
+        <v>5508493.68</v>
+      </c>
+      <c r="W3">
+        <v>864352.3199999999</v>
+      </c>
+      <c r="X3">
+        <v>6</v>
+      </c>
+      <c r="Y3">
+        <v>3049</v>
+      </c>
+      <c r="Z3">
+        <v>54</v>
+      </c>
+      <c r="AA3">
+        <v>10919</v>
+      </c>
+      <c r="AB3">
+        <v>3870</v>
+      </c>
+      <c r="AD3">
+        <v>127</v>
+      </c>
+      <c r="AE3">
+        <v>29778521</v>
+      </c>
+      <c r="AF3">
+        <v>9893397962</v>
+      </c>
+      <c r="AG3">
+        <v>371565218</v>
+      </c>
+      <c r="AH3">
+        <v>52786438244</v>
+      </c>
+      <c r="AI3">
+        <v>28608572636</v>
+      </c>
+      <c r="AK3">
+        <v>1405493217</v>
+      </c>
+      <c r="AL3">
+        <v>4963086.83</v>
+      </c>
+      <c r="AM3">
+        <v>3296700.42</v>
+      </c>
+      <c r="AN3">
+        <v>6880837.37</v>
+      </c>
+      <c r="AO3">
+        <v>4969070.72</v>
+      </c>
+      <c r="AP3">
+        <v>7417312.07</v>
+      </c>
+      <c r="AR3">
+        <v>11066875.72</v>
+      </c>
+      <c r="AS3">
+        <v>3514.66</v>
+      </c>
+      <c r="AT3">
+        <v>1280354.33</v>
+      </c>
+      <c r="AU3">
+        <v>42428.35</v>
+      </c>
+      <c r="AV3">
+        <v>6682406.27</v>
+      </c>
+      <c r="AW3">
+        <v>3427583.28</v>
+      </c>
+      <c r="AY3">
+        <v>156276.27</v>
+      </c>
+      <c r="AZ3">
         <v>470</v>
       </c>
-      <c r="HF2" t="s">
-        <v>473</v>
-      </c>
-      <c r="HG2" t="s">
-        <v>476</v>
-      </c>
-      <c r="HH2" t="s">
-        <v>478</v>
-      </c>
-      <c r="HI2" t="s">
-        <v>481</v>
-      </c>
-      <c r="HJ2" t="s">
-        <v>484</v>
-      </c>
-      <c r="HK2" t="s">
-        <v>486</v>
-      </c>
-      <c r="HL2" t="s">
-        <v>489</v>
-      </c>
-      <c r="HM2" t="s">
-        <v>492</v>
-      </c>
-      <c r="HN2" t="s">
-        <v>494</v>
-      </c>
-      <c r="HO2" t="s">
-        <v>497</v>
-      </c>
-      <c r="HP2" t="s">
-        <v>500</v>
-      </c>
-      <c r="HQ2" t="s">
-        <v>502</v>
-      </c>
-      <c r="HR2" t="s">
-        <v>504</v>
-      </c>
-      <c r="HS2" t="s">
-        <v>506</v>
-      </c>
-      <c r="HT2" t="s">
-        <v>508</v>
-      </c>
-      <c r="HU2" t="s">
-        <v>510</v>
-      </c>
-      <c r="HV2" t="s">
-        <v>512</v>
-      </c>
-      <c r="HW2" t="s">
-        <v>513</v>
-      </c>
-      <c r="HX2" t="s">
-        <v>514</v>
-      </c>
-      <c r="HY2" t="s">
-        <v>515</v>
-      </c>
-      <c r="HZ2" t="s">
-        <v>517</v>
-      </c>
-      <c r="IA2" t="s">
-        <v>519</v>
-      </c>
-      <c r="IB2" t="s">
-        <v>521</v>
-      </c>
-      <c r="IC2" t="s">
-        <v>523</v>
-      </c>
-      <c r="ID2" t="s">
-        <v>525</v>
-      </c>
-      <c r="IE2" t="s">
-        <v>527</v>
-      </c>
-      <c r="IF2" t="s">
-        <v>529</v>
-      </c>
-      <c r="IG2" t="s">
-        <v>531</v>
-      </c>
-      <c r="IH2" t="s">
-        <v>533</v>
-      </c>
-      <c r="II2" t="s">
-        <v>535</v>
-      </c>
-      <c r="IJ2" t="s">
-        <v>537</v>
-      </c>
-      <c r="IK2" t="s">
-        <v>539</v>
-      </c>
-      <c r="IL2" t="s">
-        <v>541</v>
-      </c>
-      <c r="IM2" t="s">
-        <v>543</v>
-      </c>
-      <c r="IN2" t="s">
-        <v>545</v>
-      </c>
-      <c r="IO2" t="s">
-        <v>547</v>
-      </c>
-      <c r="IP2" t="s">
-        <v>549</v>
-      </c>
-      <c r="IQ2" t="s">
-        <v>551</v>
-      </c>
-      <c r="IR2" t="s">
-        <v>553</v>
-      </c>
-      <c r="IS2" t="s">
-        <v>555</v>
-      </c>
-      <c r="IT2" t="s">
-        <v>557</v>
-      </c>
-      <c r="IU2" t="s">
-        <v>559</v>
-      </c>
-      <c r="IV2" t="s">
-        <v>561</v>
-      </c>
-      <c r="IW2" t="s">
-        <v>563</v>
-      </c>
-      <c r="IX2" t="s">
-        <v>565</v>
-      </c>
-      <c r="IY2" t="s">
-        <v>567</v>
-      </c>
-      <c r="IZ2" t="s">
-        <v>569</v>
-      </c>
-      <c r="JA2" t="s">
-        <v>571</v>
-      </c>
-      <c r="JB2" t="s">
-        <v>572</v>
-      </c>
-      <c r="JC2" t="s">
-        <v>573</v>
-      </c>
-      <c r="JD2" t="s">
-        <v>574</v>
-      </c>
-      <c r="JE2" t="s">
-        <v>576</v>
-      </c>
-      <c r="JF2" t="s">
-        <v>578</v>
-      </c>
-      <c r="JG2" t="s">
-        <v>580</v>
-      </c>
-      <c r="JH2" t="s">
-        <v>582</v>
-      </c>
-      <c r="JI2" t="s">
-        <v>584</v>
-      </c>
-      <c r="JJ2" t="s">
-        <v>586</v>
-      </c>
-      <c r="JK2" t="s">
-        <v>588</v>
-      </c>
-      <c r="JL2" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="3" spans="1:272">
-      <c r="A3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B3">
-        <v>32233124495</v>
-      </c>
-      <c r="C3">
-        <v>5994288.49</v>
-      </c>
-      <c r="D3">
-        <v>6114</v>
-      </c>
-      <c r="E3">
-        <v>39</v>
-      </c>
-      <c r="F3" s="2">
-        <v>45512</v>
-      </c>
-      <c r="G3" t="s">
-        <v>275</v>
-      </c>
-      <c r="H3">
-        <v>3897</v>
-      </c>
-      <c r="I3">
-        <v>22</v>
-      </c>
-      <c r="J3">
-        <v>1708</v>
-      </c>
-      <c r="K3">
-        <v>487</v>
-      </c>
-      <c r="L3">
-        <v>22975702753</v>
-      </c>
-      <c r="M3">
-        <v>121570001</v>
-      </c>
-      <c r="N3">
-        <v>7318348955</v>
-      </c>
-      <c r="O3">
-        <v>1817502786</v>
-      </c>
-      <c r="P3">
-        <v>6008290.47</v>
-      </c>
-      <c r="Q3">
-        <v>5525909.14</v>
-      </c>
-      <c r="R3">
-        <v>4652478.67</v>
-      </c>
-      <c r="S3">
-        <v>3786464.14</v>
-      </c>
-      <c r="T3">
-        <v>2124968.69</v>
-      </c>
-      <c r="U3">
-        <v>7767.3</v>
-      </c>
-      <c r="V3">
-        <v>3635725.62</v>
-      </c>
-      <c r="W3">
-        <v>225826.87</v>
-      </c>
-      <c r="X3">
+      <c r="BA3">
+        <v>59</v>
+      </c>
+      <c r="BB3">
         <v>1</v>
       </c>
-      <c r="Y3">
-        <v>1176</v>
-      </c>
-      <c r="AA3">
-        <v>1250</v>
-      </c>
-      <c r="AB3">
-        <v>695</v>
-      </c>
-      <c r="AC3">
-        <v>2</v>
-      </c>
-      <c r="AD3">
-        <v>10500000</v>
-      </c>
-      <c r="AE3">
-        <v>4985674842</v>
-      </c>
-      <c r="AG3">
-        <v>7636316276</v>
-      </c>
-      <c r="AH3">
-        <v>7288707699</v>
-      </c>
-      <c r="AI3">
-        <v>32200000</v>
-      </c>
-      <c r="AJ3">
-        <v>10500000</v>
-      </c>
-      <c r="AK3">
-        <v>4316601.59</v>
-      </c>
-      <c r="AM3">
-        <v>6203343.85</v>
-      </c>
-      <c r="AN3">
-        <v>10687254.69</v>
-      </c>
-      <c r="AO3">
-        <v>16100000</v>
-      </c>
-      <c r="AP3">
-        <v>402.25</v>
-      </c>
-      <c r="AQ3">
-        <v>444543.6</v>
-      </c>
-      <c r="AS3">
-        <v>693839.92</v>
-      </c>
-      <c r="AT3">
-        <v>582578.63</v>
-      </c>
-      <c r="AU3">
-        <v>1729.77</v>
-      </c>
-      <c r="AV3">
-        <v>659</v>
-      </c>
-      <c r="AX3">
+      <c r="BC3">
+        <v>31</v>
+      </c>
+      <c r="BD3">
+        <v>3</v>
+      </c>
+      <c r="BE3">
+        <v>17960</v>
+      </c>
+      <c r="BF3">
+        <v>81</v>
+      </c>
+      <c r="BG3">
+        <v>44</v>
+      </c>
+      <c r="BH3">
+        <v>546</v>
+      </c>
+      <c r="BJ3">
+        <v>53</v>
+      </c>
+      <c r="BK3">
+        <v>42</v>
+      </c>
+      <c r="BL3">
+        <v>104</v>
+      </c>
+      <c r="BM3">
+        <v>1483</v>
+      </c>
+      <c r="BN3">
         <v>1</v>
       </c>
-      <c r="AY3">
-        <v>25</v>
-      </c>
-      <c r="BA3">
-        <v>3173</v>
-      </c>
-      <c r="BB3">
-        <v>65</v>
-      </c>
-      <c r="BD3">
-        <v>22</v>
-      </c>
-      <c r="BG3">
-        <v>16</v>
-      </c>
-      <c r="BH3">
-        <v>122</v>
-      </c>
-      <c r="BI3">
-        <v>487</v>
-      </c>
-      <c r="BK3">
-        <v>13</v>
-      </c>
-      <c r="BM3">
-        <v>803</v>
-      </c>
-      <c r="BN3">
-        <v>1928</v>
-      </c>
-      <c r="BO3">
-        <v>6114</v>
-      </c>
       <c r="BP3">
-        <v>11795.32</v>
-      </c>
-      <c r="BQ3">
-        <v>16159.76</v>
+        <v>27</v>
       </c>
       <c r="BR3">
-        <v>6556.73</v>
-      </c>
-      <c r="BS3">
-        <v>13192.87</v>
+        <v>1752</v>
       </c>
       <c r="BT3">
-        <v>11989.11</v>
+        <v>7044</v>
       </c>
       <c r="BU3">
-        <v>13063.89</v>
+        <v>22220</v>
       </c>
       <c r="BV3">
-        <v>526.37</v>
+        <v>42653.27</v>
       </c>
       <c r="BW3">
-        <v>13778.4</v>
+        <v>11341.01</v>
       </c>
       <c r="BX3">
-        <v>15671.35</v>
+        <v>4867392.22</v>
       </c>
       <c r="BY3">
-        <v>25488.5</v>
+        <v>10406.24</v>
       </c>
       <c r="BZ3">
-        <v>13377.93</v>
+        <v>8157.93</v>
       </c>
       <c r="CA3">
-        <v>18136.3</v>
+        <v>11048.28</v>
       </c>
       <c r="CB3">
-        <v>20221.26</v>
+        <v>5656.13</v>
       </c>
       <c r="CC3">
-        <v>31287.33</v>
+        <v>8484.23</v>
       </c>
       <c r="CD3">
-        <v>19682.68</v>
+        <v>9180.07</v>
       </c>
       <c r="CE3">
-        <v>24805.02</v>
+        <v>13450.63</v>
       </c>
       <c r="CF3">
-        <v>94048.03720588288</v>
+        <v>16928.92</v>
       </c>
       <c r="CG3">
-        <v>124245.4874631182</v>
+        <v>14618.77</v>
       </c>
       <c r="CH3">
-        <v>52278.99154914512</v>
+        <v>10383.06</v>
       </c>
       <c r="CI3">
-        <v>101434.3406742303</v>
+        <v>16459.06</v>
       </c>
       <c r="CJ3">
-        <v>95593.16</v>
+        <v>18382163.94</v>
       </c>
       <c r="CK3">
-        <v>100442.64</v>
+        <v>20113.07</v>
       </c>
       <c r="CL3">
-        <v>4196.93</v>
+        <v>340088.7166021238</v>
       </c>
       <c r="CM3">
-        <v>105936.21</v>
+        <v>87196.1697824516</v>
       </c>
       <c r="CN3">
-        <v>124952.86</v>
+        <v>38809340.62770963</v>
       </c>
       <c r="CO3">
-        <v>195970.12</v>
+        <v>80009.14266053283</v>
       </c>
       <c r="CP3">
-        <v>106666.67</v>
+        <v>65045.89</v>
       </c>
       <c r="CQ3">
-        <v>139442.26</v>
+        <v>84945.50999999999</v>
       </c>
       <c r="CR3">
-        <v>161230.88</v>
+        <v>45098.23</v>
       </c>
       <c r="CS3">
-        <v>240554.84</v>
+        <v>65231.57</v>
       </c>
       <c r="CT3">
-        <v>156936.6</v>
+        <v>73195.73</v>
       </c>
       <c r="CU3">
-        <v>190715.19</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>277</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>280</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>282</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>284</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>286</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>289</v>
+        <v>103416.1</v>
+      </c>
+      <c r="CV3">
+        <v>134979.93</v>
+      </c>
+      <c r="CW3">
+        <v>112397.44</v>
+      </c>
+      <c r="CX3">
+        <v>82787.59</v>
+      </c>
+      <c r="CY3">
+        <v>126546.68</v>
+      </c>
+      <c r="CZ3">
+        <v>146567120.48</v>
+      </c>
+      <c r="DA3">
+        <v>154640.8</v>
       </c>
       <c r="DB3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="DC3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="DD3" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="DE3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="DF3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="DG3" t="s">
-        <v>307</v>
-      </c>
-      <c r="DH3">
-        <v>26103.13</v>
-      </c>
-      <c r="DI3">
-        <v>11488.67</v>
-      </c>
-      <c r="DK3">
-        <v>11121.67</v>
-      </c>
-      <c r="DL3">
-        <v>12770.86</v>
-      </c>
-      <c r="DM3">
-        <v>18615.14</v>
+        <v>312</v>
+      </c>
+      <c r="DH3" t="s">
+        <v>315</v>
+      </c>
+      <c r="DI3" t="s">
+        <v>318</v>
+      </c>
+      <c r="DJ3" t="s">
+        <v>322</v>
+      </c>
+      <c r="DK3" t="s">
+        <v>326</v>
+      </c>
+      <c r="DL3" t="s">
+        <v>329</v>
+      </c>
+      <c r="DM3" t="s">
+        <v>332</v>
       </c>
       <c r="DN3">
-        <v>26103.13</v>
+        <v>8425.74</v>
       </c>
       <c r="DO3">
-        <v>12450.3</v>
+        <v>7918.66</v>
+      </c>
+      <c r="DP3">
+        <v>8735.780000000001</v>
       </c>
       <c r="DQ3">
-        <v>11274.96</v>
+        <v>8119.53</v>
       </c>
       <c r="DR3">
-        <v>12414.56</v>
-      </c>
-      <c r="DS3">
-        <v>18615.14</v>
+        <v>8394.98</v>
       </c>
       <c r="DT3">
-        <v>26103.13</v>
+        <v>8852.530000000001</v>
       </c>
       <c r="DU3">
-        <v>15595.82</v>
+        <v>8604.290000000001</v>
+      </c>
+      <c r="DV3">
+        <v>8052.99</v>
       </c>
       <c r="DW3">
-        <v>13955.32</v>
+        <v>8627.58</v>
       </c>
       <c r="DX3">
-        <v>15251.15</v>
+        <v>8098.93</v>
       </c>
       <c r="DY3">
-        <v>18615.14</v>
-      </c>
-      <c r="DZ3">
-        <v>26103.13</v>
+        <v>8391.209999999999</v>
       </c>
       <c r="EA3">
-        <v>18590.55</v>
+        <v>8905.469999999999</v>
+      </c>
+      <c r="EB3">
+        <v>8817.67</v>
       </c>
       <c r="EC3">
-        <v>18287.85</v>
+        <v>9091.65</v>
       </c>
       <c r="ED3">
-        <v>22100.98</v>
+        <v>9575</v>
       </c>
       <c r="EE3">
-        <v>18615.14</v>
-      </c>
-      <c r="EF3" t="s">
-        <v>310</v>
-      </c>
-      <c r="EG3" t="s">
-        <v>313</v>
-      </c>
-      <c r="EH3" t="s">
-        <v>316</v>
-      </c>
-      <c r="EI3" t="s">
-        <v>319</v>
-      </c>
-      <c r="EJ3" t="s">
-        <v>322</v>
-      </c>
-      <c r="EK3" t="s">
-        <v>325</v>
-      </c>
-      <c r="EL3" t="s">
-        <v>328</v>
-      </c>
-      <c r="EM3" t="s">
-        <v>331</v>
-      </c>
-      <c r="EN3" t="s">
-        <v>334</v>
-      </c>
-      <c r="EO3" t="s">
-        <v>337</v>
+        <v>9029.139999999999</v>
+      </c>
+      <c r="EF3">
+        <v>9613.360000000001</v>
+      </c>
+      <c r="EH3">
+        <v>9576.09</v>
+      </c>
+      <c r="EI3">
+        <v>9124.360000000001</v>
+      </c>
+      <c r="EJ3">
+        <v>10096.78</v>
+      </c>
+      <c r="EK3">
+        <v>9766.73</v>
+      </c>
+      <c r="EL3">
+        <v>10178.73</v>
+      </c>
+      <c r="EM3">
+        <v>10890.07</v>
+      </c>
+      <c r="EO3">
+        <v>11176.41</v>
       </c>
       <c r="EP3" t="s">
+        <v>336</v>
+      </c>
+      <c r="EQ3" t="s">
         <v>340</v>
       </c>
-      <c r="EQ3" t="s">
+      <c r="ER3" t="s">
         <v>343</v>
       </c>
-      <c r="ER3" t="s">
+      <c r="ES3" t="s">
         <v>346</v>
       </c>
-      <c r="ES3" t="s">
-        <v>349</v>
-      </c>
       <c r="ET3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="EU3" t="s">
         <v>354</v>
@@ -4197,723 +4119,1526 @@
         <v>357</v>
       </c>
       <c r="EW3" t="s">
-        <v>359</v>
+        <v>360</v>
+      </c>
+      <c r="EX3" t="s">
+        <v>364</v>
       </c>
       <c r="EY3" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="EZ3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="FA3" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="FB3" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="FC3" t="s">
-        <v>370</v>
+        <v>382</v>
+      </c>
+      <c r="FD3" t="s">
+        <v>384</v>
       </c>
       <c r="FE3" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="FF3" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="FG3" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="FH3" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="FI3" t="s">
-        <v>381</v>
-      </c>
-      <c r="FK3" t="s">
-        <v>384</v>
+        <v>397</v>
+      </c>
+      <c r="FJ3" t="s">
+        <v>400</v>
       </c>
       <c r="FL3" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="FM3" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="FN3" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="FO3" t="s">
-        <v>391</v>
+        <v>410</v>
+      </c>
+      <c r="FP3" t="s">
+        <v>412</v>
       </c>
       <c r="FQ3" t="s">
-        <v>394</v>
-      </c>
-      <c r="FR3" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="FS3" t="s">
-        <v>398</v>
-      </c>
-      <c r="FT3">
+        <v>418</v>
+      </c>
+      <c r="FT3" t="s">
+        <v>420</v>
+      </c>
+      <c r="FU3" t="s">
+        <v>423</v>
+      </c>
+      <c r="FV3" t="s">
+        <v>425</v>
+      </c>
+      <c r="FW3" t="s">
+        <v>427</v>
+      </c>
+      <c r="FX3" t="s">
+        <v>430</v>
+      </c>
+      <c r="FZ3" t="s">
+        <v>433</v>
+      </c>
+      <c r="GA3" t="s">
+        <v>435</v>
+      </c>
+      <c r="GB3" t="s">
+        <v>437</v>
+      </c>
+      <c r="GC3" t="s">
+        <v>439</v>
+      </c>
+      <c r="GD3" t="s">
+        <v>441</v>
+      </c>
+      <c r="GE3" t="s">
+        <v>444</v>
+      </c>
+      <c r="GG3" t="s">
+        <v>446</v>
+      </c>
+      <c r="GH3">
+        <v>585.78</v>
+      </c>
+      <c r="GI3">
+        <v>419.93</v>
+      </c>
+      <c r="GJ3">
+        <v>785.71</v>
+      </c>
+      <c r="GK3">
+        <v>612</v>
+      </c>
+      <c r="GL3">
+        <v>885.6799999999999</v>
+      </c>
+      <c r="GN3">
+        <v>1230.52</v>
+      </c>
+      <c r="GO3" t="s">
+        <v>449</v>
+      </c>
+      <c r="GP3" t="s">
+        <v>453</v>
+      </c>
+      <c r="GQ3" t="s">
+        <v>457</v>
+      </c>
+      <c r="GR3" t="s">
+        <v>461</v>
+      </c>
+      <c r="GS3" t="s">
+        <v>465</v>
+      </c>
+      <c r="GT3" t="s">
+        <v>469</v>
+      </c>
+      <c r="GU3" t="s">
+        <v>472</v>
+      </c>
+      <c r="GV3" t="s">
+        <v>475</v>
+      </c>
+      <c r="GW3" t="s">
+        <v>478</v>
+      </c>
+      <c r="GX3" t="s">
+        <v>481</v>
+      </c>
+      <c r="GY3" t="s">
+        <v>484</v>
+      </c>
+      <c r="GZ3" t="s">
+        <v>487</v>
+      </c>
+      <c r="HA3" t="s">
+        <v>491</v>
+      </c>
+      <c r="HB3" t="s">
+        <v>494</v>
+      </c>
+      <c r="HC3" t="s">
+        <v>497</v>
+      </c>
+      <c r="HD3" t="s">
+        <v>500</v>
+      </c>
+      <c r="HE3" t="s">
+        <v>503</v>
+      </c>
+      <c r="HF3" t="s">
+        <v>506</v>
+      </c>
+      <c r="HG3" t="s">
+        <v>509</v>
+      </c>
+      <c r="HH3" t="s">
+        <v>512</v>
+      </c>
+      <c r="HI3" t="s">
+        <v>515</v>
+      </c>
+      <c r="HM3" t="s">
+        <v>520</v>
+      </c>
+      <c r="HN3" t="s">
+        <v>522</v>
+      </c>
+      <c r="HO3" t="s">
+        <v>524</v>
+      </c>
+      <c r="HP3" t="s">
+        <v>526</v>
+      </c>
+      <c r="HQ3" t="s">
+        <v>527</v>
+      </c>
+      <c r="HR3" t="s">
+        <v>528</v>
+      </c>
+      <c r="HS3" t="s">
+        <v>529</v>
+      </c>
+      <c r="HT3" t="s">
+        <v>531</v>
+      </c>
+      <c r="HU3" t="s">
+        <v>533</v>
+      </c>
+      <c r="HV3" t="s">
+        <v>535</v>
+      </c>
+      <c r="HW3" t="s">
+        <v>538</v>
+      </c>
+      <c r="HX3" t="s">
+        <v>542</v>
+      </c>
+      <c r="HY3" t="s">
+        <v>545</v>
+      </c>
+      <c r="HZ3" t="s">
+        <v>548</v>
+      </c>
+      <c r="IA3" t="s">
+        <v>552</v>
+      </c>
+      <c r="IB3" t="s">
+        <v>555</v>
+      </c>
+      <c r="IC3" t="s">
+        <v>557</v>
+      </c>
+      <c r="ID3" t="s">
+        <v>560</v>
+      </c>
+      <c r="IE3" t="s">
+        <v>563</v>
+      </c>
+      <c r="IF3" t="s">
+        <v>565</v>
+      </c>
+      <c r="IG3" t="s">
+        <v>568</v>
+      </c>
+      <c r="IH3" t="s">
+        <v>572</v>
+      </c>
+      <c r="II3" t="s">
+        <v>575</v>
+      </c>
+      <c r="IJ3" t="s">
+        <v>578</v>
+      </c>
+      <c r="IK3" t="s">
+        <v>581</v>
+      </c>
+      <c r="IL3" t="s">
+        <v>584</v>
+      </c>
+      <c r="IM3" t="s">
+        <v>587</v>
+      </c>
+      <c r="IN3" t="s">
+        <v>590</v>
+      </c>
+      <c r="IO3" t="s">
+        <v>593</v>
+      </c>
+      <c r="IP3" t="s">
+        <v>596</v>
+      </c>
+      <c r="IT3" t="s">
+        <v>600</v>
+      </c>
+      <c r="IU3" t="s">
+        <v>602</v>
+      </c>
+      <c r="IV3" t="s">
+        <v>604</v>
+      </c>
+      <c r="IW3" t="s">
+        <v>606</v>
+      </c>
+      <c r="IX3" t="s">
+        <v>607</v>
+      </c>
+      <c r="IY3" t="s">
+        <v>608</v>
+      </c>
+      <c r="IZ3" t="s">
+        <v>609</v>
+      </c>
+      <c r="JA3" t="s">
+        <v>611</v>
+      </c>
+      <c r="JB3" t="s">
+        <v>613</v>
+      </c>
+      <c r="JC3" t="s">
+        <v>615</v>
+      </c>
+      <c r="JD3" t="s">
+        <v>617</v>
+      </c>
+      <c r="JE3" t="s">
+        <v>619</v>
+      </c>
+      <c r="JF3" t="s">
+        <v>621</v>
+      </c>
+      <c r="JG3" t="s">
+        <v>623</v>
+      </c>
+      <c r="JH3" t="s">
+        <v>625</v>
+      </c>
+      <c r="JI3" t="s">
+        <v>627</v>
+      </c>
+      <c r="JJ3" t="s">
+        <v>629</v>
+      </c>
+      <c r="JK3" t="s">
+        <v>631</v>
+      </c>
+      <c r="JL3" t="s">
+        <v>633</v>
+      </c>
+      <c r="JM3" t="s">
+        <v>635</v>
+      </c>
+      <c r="JN3" t="s">
+        <v>637</v>
+      </c>
+      <c r="JO3" t="s">
+        <v>639</v>
+      </c>
+      <c r="JP3" t="s">
+        <v>641</v>
+      </c>
+      <c r="JQ3" t="s">
+        <v>643</v>
+      </c>
+      <c r="JR3" t="s">
+        <v>645</v>
+      </c>
+      <c r="JS3" t="s">
+        <v>647</v>
+      </c>
+      <c r="JT3" t="s">
+        <v>649</v>
+      </c>
+      <c r="JU3" t="s">
+        <v>651</v>
+      </c>
+      <c r="JV3" t="s">
+        <v>653</v>
+      </c>
+      <c r="JW3" t="s">
+        <v>654</v>
+      </c>
+      <c r="JX3" t="s">
+        <v>655</v>
+      </c>
+      <c r="JY3" t="s">
+        <v>656</v>
+      </c>
+      <c r="JZ3" t="s">
+        <v>658</v>
+      </c>
+      <c r="KA3" t="s">
+        <v>660</v>
+      </c>
+      <c r="KB3" t="s">
+        <v>662</v>
+      </c>
+      <c r="KC3" t="s">
+        <v>664</v>
+      </c>
+      <c r="KD3" t="s">
+        <v>666</v>
+      </c>
+      <c r="KE3" t="s">
+        <v>668</v>
+      </c>
+      <c r="KF3" t="s">
+        <v>670</v>
+      </c>
+      <c r="KG3" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="4" spans="1:293">
+      <c r="A4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B4">
+        <v>32233124495</v>
+      </c>
+      <c r="C4">
+        <v>5994288.49</v>
+      </c>
+      <c r="D4">
+        <v>6114</v>
+      </c>
+      <c r="E4">
+        <v>39</v>
+      </c>
+      <c r="F4" s="2">
+        <v>45512</v>
+      </c>
+      <c r="G4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H4">
+        <v>3897</v>
+      </c>
+      <c r="I4">
+        <v>22</v>
+      </c>
+      <c r="J4">
+        <v>1708</v>
+      </c>
+      <c r="K4">
+        <v>487</v>
+      </c>
+      <c r="L4">
+        <v>22975702753</v>
+      </c>
+      <c r="M4">
+        <v>121570001</v>
+      </c>
+      <c r="N4">
+        <v>7318348955</v>
+      </c>
+      <c r="O4">
+        <v>1817502786</v>
+      </c>
+      <c r="P4">
+        <v>6008290.47</v>
+      </c>
+      <c r="Q4">
+        <v>5525909.14</v>
+      </c>
+      <c r="R4">
+        <v>4652478.67</v>
+      </c>
+      <c r="S4">
+        <v>3786464.14</v>
+      </c>
+      <c r="T4">
+        <v>2124968.69</v>
+      </c>
+      <c r="U4">
+        <v>7767.3</v>
+      </c>
+      <c r="V4">
+        <v>3635725.62</v>
+      </c>
+      <c r="W4">
+        <v>225826.87</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>1176</v>
+      </c>
+      <c r="AA4">
+        <v>1250</v>
+      </c>
+      <c r="AB4">
+        <v>695</v>
+      </c>
+      <c r="AD4">
+        <v>2</v>
+      </c>
+      <c r="AE4">
+        <v>10500000</v>
+      </c>
+      <c r="AF4">
+        <v>4985674842</v>
+      </c>
+      <c r="AH4">
+        <v>7636316276</v>
+      </c>
+      <c r="AI4">
+        <v>7288707699</v>
+      </c>
+      <c r="AK4">
+        <v>32200000</v>
+      </c>
+      <c r="AL4">
+        <v>10500000</v>
+      </c>
+      <c r="AM4">
+        <v>4316601.59</v>
+      </c>
+      <c r="AO4">
+        <v>6203343.85</v>
+      </c>
+      <c r="AP4">
+        <v>10687254.69</v>
+      </c>
+      <c r="AR4">
+        <v>16100000</v>
+      </c>
+      <c r="AS4">
         <v>402.25</v>
       </c>
-      <c r="FU3">
-        <v>378.01</v>
-      </c>
-      <c r="FW3">
-        <v>555.0700000000001</v>
-      </c>
-      <c r="FX3">
-        <v>838.24</v>
-      </c>
-      <c r="FY3">
-        <v>864.89</v>
-      </c>
-      <c r="FZ3" t="s">
-        <v>400</v>
-      </c>
-      <c r="GA3" t="s">
-        <v>403</v>
-      </c>
-      <c r="GB3" t="s">
-        <v>406</v>
-      </c>
-      <c r="GC3" t="s">
-        <v>409</v>
-      </c>
-      <c r="GD3" t="s">
-        <v>412</v>
-      </c>
-      <c r="GE3" t="s">
-        <v>415</v>
-      </c>
-      <c r="GF3" t="s">
-        <v>418</v>
-      </c>
-      <c r="GG3" t="s">
-        <v>421</v>
-      </c>
-      <c r="GH3" t="s">
-        <v>424</v>
-      </c>
-      <c r="GI3" t="s">
-        <v>427</v>
-      </c>
-      <c r="GJ3" t="s">
-        <v>430</v>
-      </c>
-      <c r="GK3" t="s">
-        <v>433</v>
-      </c>
-      <c r="GL3" t="s">
-        <v>436</v>
-      </c>
-      <c r="GM3" t="s">
-        <v>438</v>
-      </c>
-      <c r="GN3" t="s">
-        <v>440</v>
-      </c>
-      <c r="GO3" t="s">
-        <v>442</v>
-      </c>
-      <c r="GP3" t="s">
-        <v>444</v>
-      </c>
-      <c r="GQ3" t="s">
-        <v>446</v>
-      </c>
-      <c r="GU3" t="s">
-        <v>451</v>
-      </c>
-      <c r="GV3" t="s">
-        <v>453</v>
-      </c>
-      <c r="GW3" t="s">
-        <v>455</v>
-      </c>
-      <c r="GX3" t="s">
-        <v>457</v>
-      </c>
-      <c r="GY3" t="s">
-        <v>459</v>
-      </c>
-      <c r="GZ3" t="s">
-        <v>461</v>
-      </c>
-      <c r="HA3" t="s">
-        <v>463</v>
-      </c>
-      <c r="HB3" t="s">
-        <v>465</v>
-      </c>
-      <c r="HC3" t="s">
-        <v>467</v>
-      </c>
-      <c r="HD3" t="s">
-        <v>469</v>
-      </c>
-      <c r="HE3" t="s">
-        <v>471</v>
-      </c>
-      <c r="HF3" t="s">
-        <v>474</v>
-      </c>
-      <c r="HG3" t="s">
-        <v>477</v>
-      </c>
-      <c r="HH3" t="s">
-        <v>479</v>
-      </c>
-      <c r="HI3" t="s">
-        <v>482</v>
-      </c>
-      <c r="HJ3" t="s">
-        <v>485</v>
-      </c>
-      <c r="HK3" t="s">
+      <c r="AT4">
+        <v>444543.6</v>
+      </c>
+      <c r="AV4">
+        <v>693839.92</v>
+      </c>
+      <c r="AW4">
+        <v>582578.63</v>
+      </c>
+      <c r="AY4">
+        <v>1729.77</v>
+      </c>
+      <c r="AZ4">
+        <v>659</v>
+      </c>
+      <c r="BB4">
+        <v>1</v>
+      </c>
+      <c r="BC4">
+        <v>25</v>
+      </c>
+      <c r="BE4">
+        <v>3173</v>
+      </c>
+      <c r="BF4">
+        <v>65</v>
+      </c>
+      <c r="BH4">
+        <v>22</v>
+      </c>
+      <c r="BK4">
+        <v>16</v>
+      </c>
+      <c r="BL4">
+        <v>122</v>
+      </c>
+      <c r="BM4">
         <v>487</v>
       </c>
-      <c r="HL3" t="s">
-        <v>490</v>
-      </c>
-      <c r="HM3" t="s">
-        <v>493</v>
-      </c>
-      <c r="HN3" t="s">
-        <v>495</v>
-      </c>
-      <c r="HO3" t="s">
-        <v>498</v>
-      </c>
-      <c r="HP3" t="s">
-        <v>501</v>
-      </c>
-      <c r="HQ3" t="s">
-        <v>503</v>
-      </c>
-      <c r="HR3" t="s">
-        <v>505</v>
-      </c>
-      <c r="HS3" t="s">
-        <v>507</v>
-      </c>
-      <c r="HT3" t="s">
-        <v>509</v>
-      </c>
-      <c r="HU3" t="s">
-        <v>511</v>
-      </c>
-      <c r="HY3" t="s">
-        <v>516</v>
-      </c>
-      <c r="HZ3" t="s">
-        <v>518</v>
-      </c>
-      <c r="IA3" t="s">
-        <v>520</v>
-      </c>
-      <c r="IB3" t="s">
-        <v>522</v>
-      </c>
-      <c r="IC3" t="s">
-        <v>524</v>
-      </c>
-      <c r="ID3" t="s">
-        <v>526</v>
-      </c>
-      <c r="IE3" t="s">
-        <v>528</v>
-      </c>
-      <c r="IF3" t="s">
-        <v>530</v>
-      </c>
-      <c r="IG3" t="s">
-        <v>532</v>
-      </c>
-      <c r="IH3" t="s">
-        <v>534</v>
-      </c>
-      <c r="II3" t="s">
-        <v>536</v>
-      </c>
-      <c r="IJ3" t="s">
-        <v>538</v>
-      </c>
-      <c r="IK3" t="s">
-        <v>540</v>
-      </c>
-      <c r="IL3" t="s">
-        <v>542</v>
-      </c>
-      <c r="IM3" t="s">
-        <v>544</v>
-      </c>
-      <c r="IN3" t="s">
-        <v>546</v>
-      </c>
-      <c r="IO3" t="s">
-        <v>548</v>
-      </c>
-      <c r="IP3" t="s">
-        <v>550</v>
-      </c>
-      <c r="IQ3" t="s">
-        <v>552</v>
-      </c>
-      <c r="IR3" t="s">
-        <v>554</v>
-      </c>
-      <c r="IS3" t="s">
-        <v>556</v>
-      </c>
-      <c r="IT3" t="s">
-        <v>558</v>
-      </c>
-      <c r="IU3" t="s">
-        <v>560</v>
-      </c>
-      <c r="IV3" t="s">
-        <v>562</v>
-      </c>
-      <c r="IW3" t="s">
-        <v>564</v>
-      </c>
-      <c r="IX3" t="s">
-        <v>566</v>
-      </c>
-      <c r="IY3" t="s">
-        <v>568</v>
-      </c>
-      <c r="IZ3" t="s">
-        <v>570</v>
-      </c>
-      <c r="JD3" t="s">
-        <v>575</v>
-      </c>
-      <c r="JE3" t="s">
-        <v>577</v>
-      </c>
-      <c r="JF3" t="s">
-        <v>579</v>
-      </c>
-      <c r="JG3" t="s">
-        <v>581</v>
-      </c>
-      <c r="JH3" t="s">
-        <v>583</v>
-      </c>
-      <c r="JI3" t="s">
-        <v>585</v>
-      </c>
-      <c r="JJ3" t="s">
-        <v>587</v>
-      </c>
-      <c r="JK3" t="s">
-        <v>589</v>
-      </c>
-      <c r="JL3" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="4" spans="1:272">
-      <c r="A4" t="s">
-        <v>274</v>
-      </c>
-      <c r="B4">
-        <v>182561381</v>
-      </c>
-      <c r="C4">
-        <v>1154062.58</v>
-      </c>
-      <c r="D4">
-        <v>682</v>
-      </c>
-      <c r="F4" s="2">
-        <v>45434</v>
-      </c>
-      <c r="G4" t="s">
-        <v>275</v>
-      </c>
-      <c r="H4">
-        <v>9</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>662</v>
-      </c>
-      <c r="K4">
-        <v>9</v>
-      </c>
-      <c r="L4">
-        <v>14000000</v>
-      </c>
-      <c r="M4">
-        <v>1198000</v>
-      </c>
-      <c r="N4">
-        <v>161174381</v>
-      </c>
-      <c r="O4">
-        <v>6189000</v>
-      </c>
-      <c r="P4">
-        <v>1555555.56</v>
-      </c>
-      <c r="Q4">
-        <v>599000</v>
-      </c>
-      <c r="R4">
-        <v>270426.81</v>
-      </c>
-      <c r="S4">
-        <v>687666.67</v>
-      </c>
-      <c r="T4">
-        <v>5265.21</v>
-      </c>
-      <c r="U4">
-        <v>3852.01</v>
-      </c>
-      <c r="V4">
-        <v>1128127.05</v>
-      </c>
-      <c r="W4">
-        <v>16818.32</v>
-      </c>
-      <c r="AA4">
-        <v>9</v>
-      </c>
-      <c r="AG4">
-        <v>14000000</v>
-      </c>
-      <c r="AM4">
-        <v>1555555.56</v>
-      </c>
-      <c r="AS4">
-        <v>5265.21</v>
-      </c>
-      <c r="AY4">
-        <v>9</v>
-      </c>
-      <c r="BA4">
-        <v>9</v>
-      </c>
-      <c r="BD4">
-        <v>2</v>
-      </c>
-      <c r="BE4">
-        <v>662</v>
-      </c>
-      <c r="BM4">
-        <v>113</v>
-      </c>
-      <c r="BN4">
-        <v>746</v>
-      </c>
       <c r="BO4">
-        <v>682</v>
-      </c>
-      <c r="BP4">
-        <v>2658.96</v>
-      </c>
-      <c r="BQ4">
-        <v>420</v>
+        <v>13</v>
       </c>
       <c r="BR4">
-        <v>161.2</v>
-      </c>
-      <c r="BS4">
-        <v>372.35</v>
+        <v>803</v>
       </c>
       <c r="BT4">
-        <v>2564</v>
+        <v>1928</v>
       </c>
       <c r="BU4">
-        <v>420</v>
+        <v>6114</v>
       </c>
       <c r="BV4">
-        <v>100.24</v>
+        <v>11795.32</v>
       </c>
       <c r="BW4">
-        <v>344.64</v>
+        <v>16159.76</v>
       </c>
       <c r="BX4">
-        <v>2564</v>
+        <v>6556.73</v>
       </c>
       <c r="BY4">
-        <v>535.47</v>
+        <v>13192.87</v>
       </c>
       <c r="BZ4">
-        <v>188.88</v>
+        <v>11989.11</v>
       </c>
       <c r="CA4">
-        <v>391.1</v>
+        <v>13063.89</v>
       </c>
       <c r="CB4">
-        <v>2734.93</v>
+        <v>526.37</v>
       </c>
       <c r="CC4">
-        <v>604.76</v>
+        <v>13778.4</v>
       </c>
       <c r="CD4">
-        <v>233.33</v>
+        <v>15671.35</v>
       </c>
       <c r="CE4">
-        <v>570.79</v>
+        <v>25488.5</v>
       </c>
       <c r="CF4">
-        <v>21200.79805861264</v>
+        <v>13377.93</v>
       </c>
       <c r="CG4">
-        <v>3229.234396738888</v>
+        <v>18136.3</v>
       </c>
       <c r="CH4">
-        <v>1285.314907867587</v>
+        <v>20221.26</v>
       </c>
       <c r="CI4">
-        <v>2862.821500102894</v>
+        <v>31287.33</v>
       </c>
       <c r="CJ4">
-        <v>20443.63</v>
+        <v>19682.68</v>
       </c>
       <c r="CK4">
-        <v>3229.23</v>
+        <v>24805.02</v>
       </c>
       <c r="CL4">
-        <v>799.22</v>
+        <v>94048.03720588288</v>
       </c>
       <c r="CM4">
-        <v>2649.79</v>
+        <v>124245.4874631182</v>
       </c>
       <c r="CN4">
-        <v>20443.63</v>
+        <v>52278.99154914512</v>
       </c>
       <c r="CO4">
-        <v>4117.04</v>
+        <v>101434.3406742303</v>
       </c>
       <c r="CP4">
-        <v>1506.02</v>
+        <v>95593.16</v>
       </c>
       <c r="CQ4">
-        <v>3006.98</v>
+        <v>100442.64</v>
       </c>
       <c r="CR4">
-        <v>21806.54</v>
+        <v>4196.93</v>
       </c>
       <c r="CS4">
-        <v>4649.72</v>
+        <v>105936.21</v>
       </c>
       <c r="CT4">
-        <v>1860.43</v>
+        <v>124952.86</v>
       </c>
       <c r="CU4">
-        <v>4388.55</v>
-      </c>
-      <c r="CV4" t="s">
-        <v>278</v>
-      </c>
-      <c r="CW4" t="s">
-        <v>278</v>
-      </c>
-      <c r="CX4" t="s">
-        <v>278</v>
-      </c>
-      <c r="CY4" t="s">
-        <v>278</v>
-      </c>
-      <c r="CZ4" t="s">
-        <v>287</v>
-      </c>
-      <c r="DA4" t="s">
-        <v>290</v>
+        <v>195970.12</v>
+      </c>
+      <c r="CV4">
+        <v>106666.67</v>
+      </c>
+      <c r="CW4">
+        <v>139442.26</v>
+      </c>
+      <c r="CX4">
+        <v>161230.88</v>
+      </c>
+      <c r="CY4">
+        <v>240554.84</v>
+      </c>
+      <c r="CZ4">
+        <v>156936.6</v>
+      </c>
+      <c r="DA4">
+        <v>190715.19</v>
       </c>
       <c r="DB4" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="DC4" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="DD4" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="DE4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="DF4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="DG4" t="s">
-        <v>308</v>
-      </c>
-      <c r="DK4">
-        <v>2658.96</v>
+        <v>313</v>
+      </c>
+      <c r="DH4" t="s">
+        <v>316</v>
+      </c>
+      <c r="DI4" t="s">
+        <v>319</v>
+      </c>
+      <c r="DJ4" t="s">
+        <v>323</v>
+      </c>
+      <c r="DK4" t="s">
+        <v>327</v>
+      </c>
+      <c r="DL4" t="s">
+        <v>330</v>
+      </c>
+      <c r="DM4" t="s">
+        <v>333</v>
+      </c>
+      <c r="DN4">
+        <v>26103.13</v>
+      </c>
+      <c r="DO4">
+        <v>11488.67</v>
       </c>
       <c r="DQ4">
-        <v>2564</v>
-      </c>
-      <c r="DW4">
-        <v>2564</v>
+        <v>11121.67</v>
+      </c>
+      <c r="DR4">
+        <v>12770.86</v>
+      </c>
+      <c r="DT4">
+        <v>18615.14</v>
+      </c>
+      <c r="DU4">
+        <v>26103.13</v>
+      </c>
+      <c r="DV4">
+        <v>12450.3</v>
+      </c>
+      <c r="DX4">
+        <v>11274.96</v>
+      </c>
+      <c r="DY4">
+        <v>12414.56</v>
+      </c>
+      <c r="EA4">
+        <v>18615.14</v>
+      </c>
+      <c r="EB4">
+        <v>26103.13</v>
       </c>
       <c r="EC4">
-        <v>2734.93</v>
-      </c>
-      <c r="EF4" t="s">
-        <v>311</v>
-      </c>
-      <c r="EG4" t="s">
-        <v>314</v>
-      </c>
-      <c r="EH4" t="s">
-        <v>317</v>
-      </c>
-      <c r="EI4" t="s">
-        <v>320</v>
-      </c>
-      <c r="EJ4" t="s">
-        <v>323</v>
-      </c>
-      <c r="EK4" t="s">
-        <v>326</v>
-      </c>
-      <c r="EL4" t="s">
-        <v>329</v>
-      </c>
-      <c r="EM4" t="s">
-        <v>332</v>
-      </c>
-      <c r="EN4" t="s">
-        <v>335</v>
-      </c>
-      <c r="EO4" t="s">
-        <v>338</v>
+        <v>15595.82</v>
+      </c>
+      <c r="EE4">
+        <v>13955.32</v>
+      </c>
+      <c r="EF4">
+        <v>15251.15</v>
+      </c>
+      <c r="EH4">
+        <v>18615.14</v>
+      </c>
+      <c r="EI4">
+        <v>26103.13</v>
+      </c>
+      <c r="EJ4">
+        <v>18590.55</v>
+      </c>
+      <c r="EL4">
+        <v>18287.85</v>
+      </c>
+      <c r="EM4">
+        <v>22100.98</v>
+      </c>
+      <c r="EO4">
+        <v>18615.14</v>
       </c>
       <c r="EP4" t="s">
+        <v>337</v>
+      </c>
+      <c r="EQ4" t="s">
         <v>341</v>
       </c>
-      <c r="EQ4" t="s">
+      <c r="ER4" t="s">
         <v>344</v>
       </c>
-      <c r="ER4" t="s">
+      <c r="ES4" t="s">
         <v>347</v>
       </c>
-      <c r="ES4" t="s">
-        <v>338</v>
-      </c>
       <c r="ET4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="EU4" t="s">
         <v>355</v>
       </c>
+      <c r="EV4" t="s">
+        <v>358</v>
+      </c>
+      <c r="EW4" t="s">
+        <v>361</v>
+      </c>
+      <c r="EX4" t="s">
+        <v>365</v>
+      </c>
       <c r="EY4" t="s">
-        <v>311</v>
+        <v>369</v>
+      </c>
+      <c r="EZ4" t="s">
+        <v>372</v>
+      </c>
+      <c r="FA4" t="s">
+        <v>375</v>
+      </c>
+      <c r="FB4" t="s">
+        <v>379</v>
+      </c>
+      <c r="FC4" t="s">
+        <v>383</v>
+      </c>
+      <c r="FD4" t="s">
+        <v>385</v>
       </c>
       <c r="FE4" t="s">
-        <v>323</v>
-      </c>
-      <c r="FK4" t="s">
-        <v>335</v>
+        <v>388</v>
+      </c>
+      <c r="FF4" t="s">
+        <v>391</v>
+      </c>
+      <c r="FG4" t="s">
+        <v>394</v>
+      </c>
+      <c r="FI4" t="s">
+        <v>398</v>
+      </c>
+      <c r="FJ4" t="s">
+        <v>401</v>
+      </c>
+      <c r="FL4" t="s">
+        <v>404</v>
+      </c>
+      <c r="FM4" t="s">
+        <v>406</v>
+      </c>
+      <c r="FN4" t="s">
+        <v>409</v>
+      </c>
+      <c r="FP4" t="s">
+        <v>413</v>
       </c>
       <c r="FQ4" t="s">
-        <v>347</v>
-      </c>
-      <c r="FW4">
+        <v>416</v>
+      </c>
+      <c r="FS4" t="s">
+        <v>419</v>
+      </c>
+      <c r="FT4" t="s">
+        <v>421</v>
+      </c>
+      <c r="FU4" t="s">
+        <v>424</v>
+      </c>
+      <c r="FW4" t="s">
+        <v>428</v>
+      </c>
+      <c r="FX4" t="s">
+        <v>431</v>
+      </c>
+      <c r="FZ4" t="s">
+        <v>434</v>
+      </c>
+      <c r="GA4" t="s">
+        <v>421</v>
+      </c>
+      <c r="GB4" t="s">
+        <v>438</v>
+      </c>
+      <c r="GD4" t="s">
+        <v>442</v>
+      </c>
+      <c r="GE4" t="s">
+        <v>445</v>
+      </c>
+      <c r="GG4" t="s">
+        <v>447</v>
+      </c>
+      <c r="GH4">
+        <v>402.25</v>
+      </c>
+      <c r="GI4">
+        <v>378.01</v>
+      </c>
+      <c r="GK4">
+        <v>555.0700000000001</v>
+      </c>
+      <c r="GL4">
+        <v>838.24</v>
+      </c>
+      <c r="GN4">
+        <v>864.89</v>
+      </c>
+      <c r="GO4" t="s">
+        <v>450</v>
+      </c>
+      <c r="GP4" t="s">
+        <v>454</v>
+      </c>
+      <c r="GQ4" t="s">
+        <v>458</v>
+      </c>
+      <c r="GR4" t="s">
+        <v>462</v>
+      </c>
+      <c r="GS4" t="s">
+        <v>466</v>
+      </c>
+      <c r="GT4" t="s">
+        <v>470</v>
+      </c>
+      <c r="GU4" t="s">
+        <v>473</v>
+      </c>
+      <c r="GV4" t="s">
+        <v>476</v>
+      </c>
+      <c r="GW4" t="s">
+        <v>479</v>
+      </c>
+      <c r="GX4" t="s">
+        <v>482</v>
+      </c>
+      <c r="GY4" t="s">
+        <v>485</v>
+      </c>
+      <c r="GZ4" t="s">
+        <v>488</v>
+      </c>
+      <c r="HA4" t="s">
+        <v>492</v>
+      </c>
+      <c r="HB4" t="s">
+        <v>495</v>
+      </c>
+      <c r="HC4" t="s">
+        <v>498</v>
+      </c>
+      <c r="HD4" t="s">
+        <v>501</v>
+      </c>
+      <c r="HE4" t="s">
+        <v>504</v>
+      </c>
+      <c r="HF4" t="s">
+        <v>507</v>
+      </c>
+      <c r="HG4" t="s">
+        <v>510</v>
+      </c>
+      <c r="HH4" t="s">
+        <v>513</v>
+      </c>
+      <c r="HI4" t="s">
+        <v>516</v>
+      </c>
+      <c r="HM4" t="s">
+        <v>521</v>
+      </c>
+      <c r="HN4" t="s">
+        <v>523</v>
+      </c>
+      <c r="HO4" t="s">
+        <v>525</v>
+      </c>
+      <c r="HS4" t="s">
+        <v>530</v>
+      </c>
+      <c r="HT4" t="s">
+        <v>532</v>
+      </c>
+      <c r="HU4" t="s">
+        <v>534</v>
+      </c>
+      <c r="HV4" t="s">
+        <v>536</v>
+      </c>
+      <c r="HW4" t="s">
+        <v>539</v>
+      </c>
+      <c r="HX4" t="s">
+        <v>543</v>
+      </c>
+      <c r="HY4" t="s">
+        <v>546</v>
+      </c>
+      <c r="HZ4" t="s">
+        <v>549</v>
+      </c>
+      <c r="IA4" t="s">
+        <v>553</v>
+      </c>
+      <c r="IB4" t="s">
+        <v>556</v>
+      </c>
+      <c r="IC4" t="s">
+        <v>558</v>
+      </c>
+      <c r="ID4" t="s">
+        <v>561</v>
+      </c>
+      <c r="IE4" t="s">
+        <v>564</v>
+      </c>
+      <c r="IF4" t="s">
+        <v>566</v>
+      </c>
+      <c r="IG4" t="s">
+        <v>569</v>
+      </c>
+      <c r="IH4" t="s">
+        <v>573</v>
+      </c>
+      <c r="II4" t="s">
+        <v>576</v>
+      </c>
+      <c r="IJ4" t="s">
+        <v>579</v>
+      </c>
+      <c r="IK4" t="s">
+        <v>582</v>
+      </c>
+      <c r="IL4" t="s">
+        <v>585</v>
+      </c>
+      <c r="IM4" t="s">
+        <v>588</v>
+      </c>
+      <c r="IN4" t="s">
+        <v>591</v>
+      </c>
+      <c r="IO4" t="s">
+        <v>594</v>
+      </c>
+      <c r="IP4" t="s">
+        <v>597</v>
+      </c>
+      <c r="IT4" t="s">
+        <v>601</v>
+      </c>
+      <c r="IU4" t="s">
+        <v>603</v>
+      </c>
+      <c r="IV4" t="s">
+        <v>605</v>
+      </c>
+      <c r="IZ4" t="s">
+        <v>610</v>
+      </c>
+      <c r="JA4" t="s">
+        <v>612</v>
+      </c>
+      <c r="JB4" t="s">
+        <v>614</v>
+      </c>
+      <c r="JC4" t="s">
+        <v>616</v>
+      </c>
+      <c r="JD4" t="s">
+        <v>618</v>
+      </c>
+      <c r="JE4" t="s">
+        <v>620</v>
+      </c>
+      <c r="JF4" t="s">
+        <v>622</v>
+      </c>
+      <c r="JG4" t="s">
+        <v>624</v>
+      </c>
+      <c r="JH4" t="s">
+        <v>626</v>
+      </c>
+      <c r="JI4" t="s">
+        <v>628</v>
+      </c>
+      <c r="JJ4" t="s">
+        <v>630</v>
+      </c>
+      <c r="JK4" t="s">
+        <v>632</v>
+      </c>
+      <c r="JL4" t="s">
+        <v>634</v>
+      </c>
+      <c r="JM4" t="s">
+        <v>636</v>
+      </c>
+      <c r="JN4" t="s">
+        <v>638</v>
+      </c>
+      <c r="JO4" t="s">
+        <v>640</v>
+      </c>
+      <c r="JP4" t="s">
+        <v>642</v>
+      </c>
+      <c r="JQ4" t="s">
+        <v>644</v>
+      </c>
+      <c r="JR4" t="s">
+        <v>646</v>
+      </c>
+      <c r="JS4" t="s">
+        <v>648</v>
+      </c>
+      <c r="JT4" t="s">
+        <v>650</v>
+      </c>
+      <c r="JU4" t="s">
+        <v>652</v>
+      </c>
+      <c r="JY4" t="s">
+        <v>657</v>
+      </c>
+      <c r="JZ4" t="s">
+        <v>659</v>
+      </c>
+      <c r="KA4" t="s">
+        <v>661</v>
+      </c>
+      <c r="KB4" t="s">
+        <v>663</v>
+      </c>
+      <c r="KC4" t="s">
+        <v>665</v>
+      </c>
+      <c r="KD4" t="s">
+        <v>667</v>
+      </c>
+      <c r="KE4" t="s">
+        <v>669</v>
+      </c>
+      <c r="KF4" t="s">
+        <v>671</v>
+      </c>
+      <c r="KG4" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="5" spans="1:293">
+      <c r="A5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B5">
+        <v>182561381</v>
+      </c>
+      <c r="C5">
+        <v>1154062.58</v>
+      </c>
+      <c r="D5">
+        <v>682</v>
+      </c>
+      <c r="F5" s="2">
+        <v>45434</v>
+      </c>
+      <c r="G5" t="s">
+        <v>297</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>662</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>14000000</v>
+      </c>
+      <c r="M5">
+        <v>1198000</v>
+      </c>
+      <c r="N5">
+        <v>161174381</v>
+      </c>
+      <c r="O5">
+        <v>6189000</v>
+      </c>
+      <c r="P5">
+        <v>1555555.56</v>
+      </c>
+      <c r="Q5">
+        <v>599000</v>
+      </c>
+      <c r="R5">
+        <v>270426.81</v>
+      </c>
+      <c r="S5">
+        <v>687666.67</v>
+      </c>
+      <c r="T5">
+        <v>5265.21</v>
+      </c>
+      <c r="U5">
+        <v>3852.01</v>
+      </c>
+      <c r="V5">
+        <v>1128127.05</v>
+      </c>
+      <c r="W5">
+        <v>16818.32</v>
+      </c>
+      <c r="AA5">
+        <v>9</v>
+      </c>
+      <c r="AH5">
+        <v>14000000</v>
+      </c>
+      <c r="AO5">
+        <v>1555555.56</v>
+      </c>
+      <c r="AV5">
+        <v>5265.21</v>
+      </c>
+      <c r="BC5">
+        <v>9</v>
+      </c>
+      <c r="BE5">
+        <v>9</v>
+      </c>
+      <c r="BH5">
+        <v>2</v>
+      </c>
+      <c r="BI5">
+        <v>662</v>
+      </c>
+      <c r="BR5">
+        <v>113</v>
+      </c>
+      <c r="BT5">
+        <v>746</v>
+      </c>
+      <c r="BU5">
+        <v>682</v>
+      </c>
+      <c r="BV5">
+        <v>2658.96</v>
+      </c>
+      <c r="BW5">
+        <v>420</v>
+      </c>
+      <c r="BX5">
+        <v>161.2</v>
+      </c>
+      <c r="BY5">
+        <v>372.35</v>
+      </c>
+      <c r="BZ5">
+        <v>2564</v>
+      </c>
+      <c r="CA5">
+        <v>420</v>
+      </c>
+      <c r="CB5">
+        <v>100.24</v>
+      </c>
+      <c r="CC5">
+        <v>344.64</v>
+      </c>
+      <c r="CD5">
+        <v>2564</v>
+      </c>
+      <c r="CE5">
+        <v>535.47</v>
+      </c>
+      <c r="CF5">
+        <v>188.88</v>
+      </c>
+      <c r="CG5">
+        <v>391.1</v>
+      </c>
+      <c r="CH5">
+        <v>2734.93</v>
+      </c>
+      <c r="CI5">
+        <v>604.76</v>
+      </c>
+      <c r="CJ5">
+        <v>233.33</v>
+      </c>
+      <c r="CK5">
+        <v>570.79</v>
+      </c>
+      <c r="CL5">
+        <v>21200.79805861264</v>
+      </c>
+      <c r="CM5">
+        <v>3229.234396738888</v>
+      </c>
+      <c r="CN5">
+        <v>1285.314907867587</v>
+      </c>
+      <c r="CO5">
+        <v>2862.821500102894</v>
+      </c>
+      <c r="CP5">
+        <v>20443.63</v>
+      </c>
+      <c r="CQ5">
+        <v>3229.23</v>
+      </c>
+      <c r="CR5">
+        <v>799.22</v>
+      </c>
+      <c r="CS5">
+        <v>2649.79</v>
+      </c>
+      <c r="CT5">
+        <v>20443.63</v>
+      </c>
+      <c r="CU5">
+        <v>4117.04</v>
+      </c>
+      <c r="CV5">
+        <v>1506.02</v>
+      </c>
+      <c r="CW5">
+        <v>3006.98</v>
+      </c>
+      <c r="CX5">
+        <v>21806.54</v>
+      </c>
+      <c r="CY5">
+        <v>4649.72</v>
+      </c>
+      <c r="CZ5">
+        <v>1860.43</v>
+      </c>
+      <c r="DA5">
+        <v>4388.55</v>
+      </c>
+      <c r="DB5" t="s">
+        <v>298</v>
+      </c>
+      <c r="DC5" t="s">
+        <v>298</v>
+      </c>
+      <c r="DD5" t="s">
+        <v>298</v>
+      </c>
+      <c r="DE5" t="s">
+        <v>298</v>
+      </c>
+      <c r="DF5" t="s">
+        <v>310</v>
+      </c>
+      <c r="DG5" t="s">
+        <v>314</v>
+      </c>
+      <c r="DH5" t="s">
+        <v>317</v>
+      </c>
+      <c r="DI5" t="s">
+        <v>320</v>
+      </c>
+      <c r="DJ5" t="s">
+        <v>324</v>
+      </c>
+      <c r="DK5" t="s">
+        <v>328</v>
+      </c>
+      <c r="DL5" t="s">
+        <v>331</v>
+      </c>
+      <c r="DM5" t="s">
+        <v>334</v>
+      </c>
+      <c r="DQ5">
+        <v>2658.96</v>
+      </c>
+      <c r="DX5">
+        <v>2564</v>
+      </c>
+      <c r="EE5">
+        <v>2564</v>
+      </c>
+      <c r="EL5">
+        <v>2734.93</v>
+      </c>
+      <c r="EP5" t="s">
+        <v>338</v>
+      </c>
+      <c r="EQ5" t="s">
+        <v>342</v>
+      </c>
+      <c r="ER5" t="s">
+        <v>345</v>
+      </c>
+      <c r="ES5" t="s">
+        <v>348</v>
+      </c>
+      <c r="ET5" t="s">
+        <v>352</v>
+      </c>
+      <c r="EU5" t="s">
+        <v>356</v>
+      </c>
+      <c r="EV5" t="s">
+        <v>359</v>
+      </c>
+      <c r="EW5" t="s">
+        <v>362</v>
+      </c>
+      <c r="EX5" t="s">
+        <v>366</v>
+      </c>
+      <c r="EY5" t="s">
+        <v>370</v>
+      </c>
+      <c r="EZ5" t="s">
+        <v>373</v>
+      </c>
+      <c r="FA5" t="s">
+        <v>376</v>
+      </c>
+      <c r="FB5" t="s">
+        <v>380</v>
+      </c>
+      <c r="FC5" t="s">
+        <v>370</v>
+      </c>
+      <c r="FD5" t="s">
+        <v>386</v>
+      </c>
+      <c r="FE5" t="s">
+        <v>389</v>
+      </c>
+      <c r="FI5" t="s">
+        <v>338</v>
+      </c>
+      <c r="FP5" t="s">
+        <v>352</v>
+      </c>
+      <c r="FW5" t="s">
+        <v>366</v>
+      </c>
+      <c r="GD5" t="s">
+        <v>380</v>
+      </c>
+      <c r="GK5">
         <v>585.02</v>
       </c>
-      <c r="FZ4" t="s">
-        <v>401</v>
-      </c>
-      <c r="GA4" t="s">
-        <v>404</v>
-      </c>
-      <c r="GB4" t="s">
-        <v>407</v>
-      </c>
-      <c r="GC4" t="s">
-        <v>410</v>
-      </c>
-      <c r="GD4" t="s">
-        <v>413</v>
-      </c>
-      <c r="GE4" t="s">
-        <v>416</v>
-      </c>
-      <c r="GF4" t="s">
-        <v>419</v>
-      </c>
-      <c r="GG4" t="s">
-        <v>422</v>
-      </c>
-      <c r="GH4" t="s">
-        <v>425</v>
-      </c>
-      <c r="GI4" t="s">
-        <v>428</v>
-      </c>
-      <c r="GJ4" t="s">
-        <v>431</v>
-      </c>
-      <c r="GK4" t="s">
-        <v>434</v>
-      </c>
-      <c r="GU4" t="s">
-        <v>401</v>
-      </c>
-      <c r="GV4" t="s">
-        <v>404</v>
-      </c>
-      <c r="GW4" t="s">
-        <v>407</v>
-      </c>
-      <c r="HD4" t="s">
-        <v>299</v>
-      </c>
-      <c r="HE4" t="s">
-        <v>472</v>
-      </c>
-      <c r="HF4" t="s">
-        <v>475</v>
-      </c>
-      <c r="HG4" t="s">
-        <v>302</v>
-      </c>
-      <c r="HH4" t="s">
+      <c r="GO5" t="s">
+        <v>451</v>
+      </c>
+      <c r="GP5" t="s">
+        <v>455</v>
+      </c>
+      <c r="GQ5" t="s">
+        <v>459</v>
+      </c>
+      <c r="GR5" t="s">
+        <v>463</v>
+      </c>
+      <c r="GS5" t="s">
+        <v>467</v>
+      </c>
+      <c r="GT5" t="s">
+        <v>471</v>
+      </c>
+      <c r="GU5" t="s">
+        <v>474</v>
+      </c>
+      <c r="GV5" t="s">
+        <v>477</v>
+      </c>
+      <c r="GW5" t="s">
         <v>480</v>
       </c>
-      <c r="HI4" t="s">
+      <c r="GX5" t="s">
         <v>483</v>
       </c>
-      <c r="HJ4" t="s">
-        <v>305</v>
-      </c>
-      <c r="HK4" t="s">
-        <v>488</v>
-      </c>
-      <c r="HL4" t="s">
-        <v>491</v>
-      </c>
-      <c r="HM4" t="s">
-        <v>308</v>
-      </c>
-      <c r="HN4" t="s">
-        <v>496</v>
-      </c>
-      <c r="HO4" t="s">
-        <v>499</v>
-      </c>
-      <c r="HY4" t="s">
-        <v>299</v>
-      </c>
-      <c r="HZ4" t="s">
-        <v>472</v>
-      </c>
-      <c r="IA4" t="s">
-        <v>475</v>
-      </c>
-      <c r="IH4" t="s">
-        <v>278</v>
+      <c r="GY5" t="s">
+        <v>486</v>
+      </c>
+      <c r="GZ5" t="s">
+        <v>489</v>
+      </c>
+      <c r="HD5" t="s">
+        <v>451</v>
+      </c>
+      <c r="HE5" t="s">
+        <v>455</v>
+      </c>
+      <c r="HF5" t="s">
+        <v>459</v>
+      </c>
+      <c r="HV5" t="s">
+        <v>324</v>
+      </c>
+      <c r="HW5" t="s">
+        <v>540</v>
+      </c>
+      <c r="HX5" t="s">
+        <v>544</v>
+      </c>
+      <c r="HY5" t="s">
+        <v>328</v>
+      </c>
+      <c r="HZ5" t="s">
+        <v>550</v>
+      </c>
+      <c r="IA5" t="s">
+        <v>554</v>
+      </c>
+      <c r="IB5" t="s">
+        <v>331</v>
+      </c>
+      <c r="IC5" t="s">
+        <v>559</v>
+      </c>
+      <c r="ID5" t="s">
+        <v>562</v>
+      </c>
+      <c r="IE5" t="s">
+        <v>334</v>
+      </c>
+      <c r="IF5" t="s">
+        <v>567</v>
+      </c>
+      <c r="IG5" t="s">
+        <v>570</v>
+      </c>
+      <c r="IK5" t="s">
+        <v>324</v>
+      </c>
+      <c r="IL5" t="s">
+        <v>540</v>
+      </c>
+      <c r="IM5" t="s">
+        <v>544</v>
+      </c>
+      <c r="JC5" t="s">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
